--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\cs-tools\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492B0456-3A94-4867-8351-118E095B42D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3929EF7-EE36-4138-A156-2706A8145FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
@@ -289,9 +289,6 @@
     <t>kONO</t>
   </si>
   <si>
-    <t>LGB eSports</t>
-  </si>
-  <si>
     <t>MAD Lions</t>
   </si>
   <si>
@@ -394,9 +391,6 @@
     <t>2026-02-19T01:45:45.455Z</t>
   </si>
   <si>
-    <t>Chinggis Warrios</t>
-  </si>
-  <si>
     <t>2026-02-19T22:08:18.806Z</t>
   </si>
   <si>
@@ -896,6 +890,12 @@
   </si>
   <si>
     <t>1 star</t>
+  </si>
+  <si>
+    <t>LGB</t>
+  </si>
+  <si>
+    <t>Chinggis Warriors</t>
   </si>
 </sst>
 </file>
@@ -1273,12 +1273,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q165"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1319,19 +1319,19 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O1" t="s">
+        <v>287</v>
+      </c>
+      <c r="P1" t="s">
         <v>288</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>289</v>
       </c>
-      <c r="P1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>75</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>77</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>79</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>80</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>81</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>82</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>83</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>87</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>88</v>
       </c>
@@ -3504,9 +3504,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3545,9 +3545,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3586,9 +3586,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3627,9 +3627,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3668,9 +3668,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3709,9 +3709,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3750,9 +3750,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3791,9 +3791,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3832,9 +3832,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3873,9 +3873,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3914,9 +3914,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3955,9 +3955,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3996,9 +3996,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -4037,9 +4037,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -4078,9 +4078,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4119,9 +4119,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4160,9 +4160,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4201,9 +4201,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4242,9 +4242,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4283,9 +4283,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4324,9 +4324,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4365,9 +4365,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4406,9 +4406,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4447,9 +4447,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4485,12 +4485,12 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>114</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4526,12 +4526,12 @@
         <v>0</v>
       </c>
       <c r="M79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>116</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4567,12 +4567,12 @@
         <v>0</v>
       </c>
       <c r="M80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>118</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4608,12 +4608,12 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>120</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -4649,12 +4649,12 @@
         <v>0</v>
       </c>
       <c r="M82" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>122</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4690,12 +4690,12 @@
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>124</v>
+        <v>291</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -4731,12 +4731,12 @@
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -4772,12 +4772,12 @@
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4813,12 +4813,12 @@
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4854,12 +4854,12 @@
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -4895,12 +4895,12 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -4936,12 +4936,12 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4977,12 +4977,12 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5018,12 +5018,12 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -5059,12 +5059,12 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -5100,12 +5100,12 @@
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -5141,12 +5141,12 @@
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -5182,12 +5182,12 @@
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -5223,12 +5223,12 @@
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5264,12 +5264,12 @@
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5305,12 +5305,12 @@
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5346,12 +5346,12 @@
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5387,12 +5387,12 @@
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5428,12 +5428,12 @@
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5469,12 +5469,12 @@
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5510,12 +5510,12 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5551,12 +5551,12 @@
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5592,12 +5592,12 @@
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5633,12 +5633,12 @@
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5674,12 +5674,12 @@
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5715,12 +5715,12 @@
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5756,12 +5756,12 @@
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -5797,12 +5797,12 @@
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5838,12 +5838,12 @@
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5879,12 +5879,12 @@
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5920,12 +5920,12 @@
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5961,12 +5961,12 @@
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6002,12 +6002,12 @@
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6043,12 +6043,12 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6084,12 +6084,12 @@
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6125,12 +6125,12 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6166,12 +6166,12 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6207,12 +6207,12 @@
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6248,12 +6248,12 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6289,12 +6289,12 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6330,12 +6330,12 @@
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6371,12 +6371,12 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -6412,12 +6412,12 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -6453,12 +6453,12 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -6494,12 +6494,12 @@
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -6535,12 +6535,12 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -6576,12 +6576,12 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -6617,12 +6617,12 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -6658,12 +6658,12 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -6699,12 +6699,12 @@
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -6740,12 +6740,12 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -6781,12 +6781,12 @@
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -6822,12 +6822,12 @@
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -6863,12 +6863,12 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -6904,12 +6904,12 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -6945,12 +6945,12 @@
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -6986,12 +6986,12 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -7027,12 +7027,12 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -7068,12 +7068,12 @@
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -7109,12 +7109,12 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -7150,12 +7150,12 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7191,12 +7191,12 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7232,12 +7232,12 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7273,12 +7273,12 @@
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7314,12 +7314,12 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7355,12 +7355,12 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7396,12 +7396,12 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7437,12 +7437,12 @@
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7478,12 +7478,12 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7519,12 +7519,12 @@
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7560,12 +7560,12 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7601,12 +7601,12 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7642,12 +7642,12 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7683,12 +7683,12 @@
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7724,12 +7724,12 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7765,12 +7765,12 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -7806,12 +7806,12 @@
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7847,12 +7847,12 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -7888,12 +7888,12 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -7929,12 +7929,12 @@
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -7970,12 +7970,12 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -8011,12 +8011,12 @@
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -8052,13 +8052,13 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M165" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M54 A56:M83 B55:M55 A85:M165 B84:M84" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3929EF7-EE36-4138-A156-2706A8145FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2C67CB-58A8-4CE1-91A3-207DAC58AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="292">
   <si>
     <t>Team</t>
   </si>
@@ -61,6 +61,18 @@
     <t>LastUpdated</t>
   </si>
   <si>
+    <t>4 star</t>
+  </si>
+  <si>
+    <t>3 star</t>
+  </si>
+  <si>
+    <t>2 star</t>
+  </si>
+  <si>
+    <t>1 star</t>
+  </si>
+  <si>
     <t>The MongolZ</t>
   </si>
   <si>
@@ -73,102 +85,105 @@
     <t>none</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:50.179Z</t>
+    <t>2026-03-21T04:31:17.566Z</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Iluminar</t>
   </si>
   <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:26.612Z</t>
+  </si>
+  <si>
+    <t>Nemiga</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:46.138Z</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
     <t>Tier 3</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:37:58.230Z</t>
+    <t>2026-03-21T04:32:15.700Z</t>
+  </si>
+  <si>
+    <t>Vitality</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:36.203Z</t>
   </si>
   <si>
     <t>Liquid</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:26.757Z</t>
-  </si>
-  <si>
     <t>Titan</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:39.250Z</t>
-  </si>
-  <si>
-    <t>Nemiga</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:23.828Z</t>
+    <t>Copenhagen Flames</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:32:33.790Z</t>
   </si>
   <si>
     <t>Eternal Fire</t>
   </si>
   <si>
-    <t>EU</t>
-  </si>
-  <si>
-    <t>Elevate</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:40.257Z</t>
+    <t>2026-03-21T04:31:59.142Z</t>
+  </si>
+  <si>
+    <t>Falcons</t>
   </si>
   <si>
     <t>PARIVISION</t>
   </si>
   <si>
-    <t>Vitality</t>
-  </si>
-  <si>
     <t>Natus Vincere</t>
   </si>
   <si>
+    <t>Cloud9</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:32:26.020Z</t>
+  </si>
+  <si>
     <t>Heroic</t>
   </si>
   <si>
-    <t>2026-02-28T06:38:48.174Z</t>
-  </si>
-  <si>
-    <t>Copenhagen Flames</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:31.762Z</t>
-  </si>
-  <si>
     <t>Verdant</t>
   </si>
   <si>
     <t>2026-02-28T06:29:24.671Z</t>
   </si>
   <si>
-    <t>Falcons</t>
+    <t>Bounty Hunters</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:59.888Z</t>
   </si>
   <si>
     <t>Spirit</t>
   </si>
   <si>
-    <t>Cloud9</t>
+    <t>The Huns</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:06.168Z</t>
   </si>
   <si>
     <t>Onyx Ravens</t>
   </si>
   <si>
-    <t>Bounty Hunters</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:28:59.888Z</t>
-  </si>
-  <si>
-    <t>The Huns</t>
-  </si>
-  <si>
-    <t>2026-02-18T21:21:06.168Z</t>
-  </si>
-  <si>
     <t>TYLOO</t>
   </si>
   <si>
@@ -202,9 +217,6 @@
     <t>00 Nation</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>100 Thieves</t>
   </si>
   <si>
@@ -289,6 +301,9 @@
     <t>kONO</t>
   </si>
   <si>
+    <t>LGB</t>
+  </si>
+  <si>
     <t>MAD Lions</t>
   </si>
   <si>
@@ -391,6 +406,9 @@
     <t>2026-02-19T01:45:45.455Z</t>
   </si>
   <si>
+    <t>Chinggis Warriors</t>
+  </si>
+  <si>
     <t>2026-02-19T22:08:18.806Z</t>
   </si>
   <si>
@@ -878,24 +896,6 @@
   </si>
   <si>
     <t>2026-02-19T01:45:20.251Z</t>
-  </si>
-  <si>
-    <t>4 star</t>
-  </si>
-  <si>
-    <t>3 star</t>
-  </si>
-  <si>
-    <t>2 star</t>
-  </si>
-  <si>
-    <t>1 star</t>
-  </si>
-  <si>
-    <t>LGB</t>
-  </si>
-  <si>
-    <t>Chinggis Warriors</t>
   </si>
 </sst>
 </file>
@@ -931,7 +931,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1273,12 +1274,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q165"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1319,33 +1317,33 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>287</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1103.5396883405394</v>
+        <v>1118.935353572816</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1357,118 +1355,154 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1110.4490389924551</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1094.2205166212659</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1102.2670104875274</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>1093.7510210031935</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1090.4930427442032</v>
+        <v>1087.1014484109633</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1480,36 +1514,48 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1088.1168262682929</v>
+        <v>1077.6235341337183</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1521,200 +1567,260 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1077.5224986320043</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>1075.2807088818799</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1070.290679853573</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>1073.614299461236</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>1072.1962700599079</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>1056.9314284733287</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1063.3157624288613</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1062.7199050958704</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" t="s">
-        <v>29</v>
-      </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1062.0404218180502</v>
+        <v>1051.4823754499648</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1726,159 +1832,207 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1048.6990812898496</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1048.1641215202962</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
         <v>1</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1060.4876942715719</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>1045.8673946600638</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J12" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>1056.483574632495</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>1038.7190184710753</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15">
-        <v>1034.4702257617066</v>
+        <v>1045.2899043783382</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1890,36 +2044,48 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
       <c r="E16">
-        <v>1031.7815101827721</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1931,159 +2097,207 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="N16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1017.2412711985547</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>1016.7402640066111</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1015</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" t="s">
+        <v>22</v>
+      </c>
+      <c r="O19" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20">
         <v>7</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17">
-        <v>1030.8261484839029</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18">
-        <v>1028.7948309045817</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>1017.2412711985547</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>1015</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2095,24 +2309,36 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -2136,24 +2362,36 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="N21" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -2177,24 +2415,36 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="N22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -2218,24 +2468,36 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="N23" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -2259,24 +2521,36 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -2300,24 +2574,36 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="N25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2341,24 +2627,36 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2382,24 +2680,36 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s">
+        <v>22</v>
+      </c>
+      <c r="O27" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2423,24 +2733,36 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2464,24 +2786,36 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s">
+        <v>22</v>
+      </c>
+      <c r="O29" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2505,24 +2839,36 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s">
+        <v>22</v>
+      </c>
+      <c r="O30" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2546,24 +2892,36 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s">
+        <v>22</v>
+      </c>
+      <c r="O31" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2587,24 +2945,36 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
       <c r="K32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O32" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2628,24 +2998,36 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N33" t="s">
+        <v>22</v>
+      </c>
+      <c r="O33" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2669,24 +3051,36 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s">
+        <v>22</v>
+      </c>
+      <c r="O34" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2710,24 +3104,36 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N35" t="s">
+        <v>22</v>
+      </c>
+      <c r="O35" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2751,24 +3157,36 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N36" t="s">
+        <v>22</v>
+      </c>
+      <c r="O36" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2792,24 +3210,36 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>22</v>
+      </c>
+      <c r="O37" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2833,24 +3263,36 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>22</v>
+      </c>
+      <c r="O38" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2874,24 +3316,36 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
+        <v>22</v>
+      </c>
+      <c r="O39" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2915,24 +3369,36 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
+        <v>22</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2956,24 +3422,36 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
+        <v>22</v>
+      </c>
+      <c r="O41" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2997,24 +3475,36 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N42" t="s">
+        <v>22</v>
+      </c>
+      <c r="O42" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3038,24 +3528,36 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N43" t="s">
+        <v>22</v>
+      </c>
+      <c r="O43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3079,24 +3581,36 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J44" t="s">
-        <v>15</v>
-      </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N44" t="s">
+        <v>22</v>
+      </c>
+      <c r="O44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3120,24 +3634,36 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N45" t="s">
+        <v>22</v>
+      </c>
+      <c r="O45" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3161,24 +3687,36 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J46" t="s">
-        <v>15</v>
-      </c>
       <c r="K46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N46" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" t="s">
+        <v>22</v>
+      </c>
+      <c r="P46" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3202,24 +3740,36 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K47" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N47" t="s">
+        <v>22</v>
+      </c>
+      <c r="O47" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3243,24 +3793,36 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3284,24 +3846,36 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N49" t="s">
+        <v>22</v>
+      </c>
+      <c r="O49" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3325,24 +3899,36 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K50" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N50" t="s">
+        <v>22</v>
+      </c>
+      <c r="O50" t="s">
+        <v>22</v>
+      </c>
+      <c r="P50" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3366,24 +3952,36 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N51" t="s">
+        <v>22</v>
+      </c>
+      <c r="O51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P51" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3407,24 +4005,36 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N52" t="s">
+        <v>22</v>
+      </c>
+      <c r="O52" t="s">
+        <v>22</v>
+      </c>
+      <c r="P52" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3448,24 +4058,36 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K53" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N53" t="s">
+        <v>22</v>
+      </c>
+      <c r="O53" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3489,24 +4111,36 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
       <c r="K54" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N54" t="s">
+        <v>22</v>
+      </c>
+      <c r="O54" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3530,24 +4164,36 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
       <c r="K55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N55" t="s">
+        <v>22</v>
+      </c>
+      <c r="O55" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3571,24 +4217,36 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N56" t="s">
+        <v>22</v>
+      </c>
+      <c r="O56" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3612,24 +4270,36 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
-      </c>
-      <c r="J57" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N57" t="s">
+        <v>22</v>
+      </c>
+      <c r="O57" t="s">
+        <v>22</v>
+      </c>
+      <c r="P57" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3653,24 +4323,36 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
-      </c>
-      <c r="J58" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N58" t="s">
+        <v>22</v>
+      </c>
+      <c r="O58" t="s">
+        <v>22</v>
+      </c>
+      <c r="P58" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3694,24 +4376,36 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N59" t="s">
+        <v>22</v>
+      </c>
+      <c r="O59" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3735,24 +4429,36 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N60" t="s">
+        <v>22</v>
+      </c>
+      <c r="O60" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3776,24 +4482,36 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N61" t="s">
+        <v>22</v>
+      </c>
+      <c r="O61" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3817,24 +4535,36 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K62" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N62" t="s">
+        <v>22</v>
+      </c>
+      <c r="O62" t="s">
+        <v>22</v>
+      </c>
+      <c r="P62" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3858,24 +4588,36 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K63" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N63" t="s">
+        <v>22</v>
+      </c>
+      <c r="O63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P63" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3899,24 +4641,36 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K64" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N64" t="s">
+        <v>22</v>
+      </c>
+      <c r="O64" t="s">
+        <v>22</v>
+      </c>
+      <c r="P64" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3940,24 +4694,36 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K65" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N65" t="s">
+        <v>22</v>
+      </c>
+      <c r="O65" t="s">
+        <v>22</v>
+      </c>
+      <c r="P65" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3981,24 +4747,36 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N66" t="s">
+        <v>22</v>
+      </c>
+      <c r="O66" t="s">
+        <v>22</v>
+      </c>
+      <c r="P66" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -4022,24 +4800,36 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N67" t="s">
+        <v>22</v>
+      </c>
+      <c r="O67" t="s">
+        <v>22</v>
+      </c>
+      <c r="P67" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -4063,24 +4853,36 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
-      </c>
-      <c r="J68" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N68" t="s">
+        <v>22</v>
+      </c>
+      <c r="O68" t="s">
+        <v>22</v>
+      </c>
+      <c r="P68" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4104,24 +4906,36 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J69" t="s">
-        <v>15</v>
-      </c>
       <c r="K69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N69" t="s">
+        <v>22</v>
+      </c>
+      <c r="O69" t="s">
+        <v>22</v>
+      </c>
+      <c r="P69" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4145,24 +4959,36 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J70" t="s">
-        <v>15</v>
-      </c>
       <c r="K70" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N70" t="s">
+        <v>22</v>
+      </c>
+      <c r="O70" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4186,24 +5012,36 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
-      </c>
-      <c r="J71" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K71" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N71" t="s">
+        <v>22</v>
+      </c>
+      <c r="O71" t="s">
+        <v>22</v>
+      </c>
+      <c r="P71" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4227,24 +5065,36 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
-      </c>
-      <c r="J72" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N72" t="s">
+        <v>22</v>
+      </c>
+      <c r="O72" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4268,24 +5118,36 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N73" t="s">
+        <v>22</v>
+      </c>
+      <c r="O73" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4309,24 +5171,36 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K74" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N74" t="s">
+        <v>22</v>
+      </c>
+      <c r="O74" t="s">
+        <v>22</v>
+      </c>
+      <c r="P74" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4350,24 +5224,36 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
-      </c>
-      <c r="J75" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N75" t="s">
+        <v>22</v>
+      </c>
+      <c r="O75" t="s">
+        <v>22</v>
+      </c>
+      <c r="P75" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4391,24 +5277,36 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N76" t="s">
+        <v>22</v>
+      </c>
+      <c r="O76" t="s">
+        <v>22</v>
+      </c>
+      <c r="P76" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4432,24 +5330,36 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
-      </c>
-      <c r="J77" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K77" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="N77" t="s">
+        <v>22</v>
+      </c>
+      <c r="O77" t="s">
+        <v>22</v>
+      </c>
+      <c r="P77" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4473,24 +5383,36 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
       <c r="K78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="N78" t="s">
+        <v>22</v>
+      </c>
+      <c r="O78" t="s">
+        <v>22</v>
+      </c>
+      <c r="P78" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4514,24 +5436,36 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K79" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+      <c r="N79" t="s">
+        <v>22</v>
+      </c>
+      <c r="O79" t="s">
+        <v>22</v>
+      </c>
+      <c r="P79" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4555,24 +5489,36 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
-      </c>
-      <c r="J80" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K80" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+      <c r="N80" t="s">
+        <v>22</v>
+      </c>
+      <c r="O80" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4596,24 +5542,36 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
-      </c>
-      <c r="J81" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="N81" t="s">
+        <v>22</v>
+      </c>
+      <c r="O81" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -4637,24 +5595,36 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
-      </c>
-      <c r="J82" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K82" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="N82" t="s">
+        <v>22</v>
+      </c>
+      <c r="O82" t="s">
+        <v>22</v>
+      </c>
+      <c r="P82" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4678,24 +5648,36 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
-      </c>
-      <c r="J83" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="N83" t="s">
+        <v>22</v>
+      </c>
+      <c r="O83" t="s">
+        <v>22</v>
+      </c>
+      <c r="P83" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>291</v>
+        <v>128</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -4719,24 +5701,36 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
       <c r="K84" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="N84" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" t="s">
+        <v>22</v>
+      </c>
+      <c r="P84" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -4760,24 +5754,36 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
-      </c>
-      <c r="J85" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K85" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+      <c r="N85" t="s">
+        <v>22</v>
+      </c>
+      <c r="O85" t="s">
+        <v>22</v>
+      </c>
+      <c r="P85" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4801,24 +5807,36 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
-      </c>
-      <c r="J86" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="N86" t="s">
+        <v>22</v>
+      </c>
+      <c r="O86" t="s">
+        <v>22</v>
+      </c>
+      <c r="P86" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4842,24 +5860,36 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
-      </c>
-      <c r="J87" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K87" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+      <c r="N87" t="s">
+        <v>22</v>
+      </c>
+      <c r="O87" t="s">
+        <v>22</v>
+      </c>
+      <c r="P87" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -4883,24 +5913,36 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
-      </c>
-      <c r="J88" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+      <c r="N88" t="s">
+        <v>22</v>
+      </c>
+      <c r="O88" t="s">
+        <v>22</v>
+      </c>
+      <c r="P88" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -4924,24 +5966,36 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
-      </c>
-      <c r="J89" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K89" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+      <c r="N89" t="s">
+        <v>22</v>
+      </c>
+      <c r="O89" t="s">
+        <v>22</v>
+      </c>
+      <c r="P89" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4965,24 +6019,36 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
-      </c>
-      <c r="J90" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K90" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+      <c r="N90" t="s">
+        <v>22</v>
+      </c>
+      <c r="O90" t="s">
+        <v>22</v>
+      </c>
+      <c r="P90" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5006,24 +6072,36 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
-      </c>
-      <c r="J91" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+      <c r="N91" t="s">
+        <v>22</v>
+      </c>
+      <c r="O91" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -5047,24 +6125,36 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
-      </c>
-      <c r="J92" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K92" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+      <c r="N92" t="s">
+        <v>22</v>
+      </c>
+      <c r="O92" t="s">
+        <v>22</v>
+      </c>
+      <c r="P92" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -5088,24 +6178,36 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
-      </c>
-      <c r="J93" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K93" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+      <c r="N93" t="s">
+        <v>22</v>
+      </c>
+      <c r="O93" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -5129,24 +6231,36 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J94" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+      <c r="N94" t="s">
+        <v>22</v>
+      </c>
+      <c r="O94" t="s">
+        <v>22</v>
+      </c>
+      <c r="P94" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -5170,24 +6284,36 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
-      </c>
-      <c r="J95" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K95" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+      <c r="N95" t="s">
+        <v>22</v>
+      </c>
+      <c r="O95" t="s">
+        <v>22</v>
+      </c>
+      <c r="P95" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -5211,24 +6337,36 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J96" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+      <c r="N96" t="s">
+        <v>22</v>
+      </c>
+      <c r="O96" t="s">
+        <v>22</v>
+      </c>
+      <c r="P96" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5252,24 +6390,36 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J97" t="s">
-        <v>15</v>
-      </c>
       <c r="K97" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+      <c r="N97" t="s">
+        <v>22</v>
+      </c>
+      <c r="O97" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5293,24 +6443,36 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
-      </c>
-      <c r="J98" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K98" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+      <c r="N98" t="s">
+        <v>22</v>
+      </c>
+      <c r="O98" t="s">
+        <v>22</v>
+      </c>
+      <c r="P98" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5334,24 +6496,36 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
+        <v>29</v>
+      </c>
+      <c r="J99" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J99" t="s">
-        <v>29</v>
-      </c>
       <c r="K99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="N99" t="s">
+        <v>22</v>
+      </c>
+      <c r="O99" t="s">
+        <v>22</v>
+      </c>
+      <c r="P99" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5375,24 +6549,36 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
-      </c>
-      <c r="J100" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K100" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="N100" t="s">
+        <v>22</v>
+      </c>
+      <c r="O100" t="s">
+        <v>22</v>
+      </c>
+      <c r="P100" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5416,24 +6602,36 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
-      </c>
-      <c r="J101" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+      <c r="N101" t="s">
+        <v>22</v>
+      </c>
+      <c r="O101" t="s">
+        <v>22</v>
+      </c>
+      <c r="P101" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5457,24 +6655,36 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
-      </c>
-      <c r="J102" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K102" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+      <c r="N102" t="s">
+        <v>22</v>
+      </c>
+      <c r="O102" t="s">
+        <v>22</v>
+      </c>
+      <c r="P102" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5498,24 +6708,36 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J103" t="s">
-        <v>15</v>
-      </c>
       <c r="K103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+      <c r="N103" t="s">
+        <v>22</v>
+      </c>
+      <c r="O103" t="s">
+        <v>22</v>
+      </c>
+      <c r="P103" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5539,24 +6761,36 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
-      </c>
-      <c r="J104" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K104" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+      <c r="N104" t="s">
+        <v>22</v>
+      </c>
+      <c r="O104" t="s">
+        <v>22</v>
+      </c>
+      <c r="P104" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5580,24 +6814,36 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
-      </c>
-      <c r="J105" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K105" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L105">
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+      <c r="N105" t="s">
+        <v>22</v>
+      </c>
+      <c r="O105" t="s">
+        <v>22</v>
+      </c>
+      <c r="P105" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5621,24 +6867,36 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
-      </c>
-      <c r="J106" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K106" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+      <c r="N106" t="s">
+        <v>22</v>
+      </c>
+      <c r="O106" t="s">
+        <v>22</v>
+      </c>
+      <c r="P106" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5662,24 +6920,36 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
-      </c>
-      <c r="J107" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K107" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+      <c r="N107" t="s">
+        <v>22</v>
+      </c>
+      <c r="O107" t="s">
+        <v>22</v>
+      </c>
+      <c r="P107" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5703,24 +6973,36 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
-      </c>
-      <c r="J108" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K108" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+      <c r="N108" t="s">
+        <v>22</v>
+      </c>
+      <c r="O108" t="s">
+        <v>22</v>
+      </c>
+      <c r="P108" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5744,24 +7026,36 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
-      </c>
-      <c r="J109" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K109" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+      <c r="N109" t="s">
+        <v>22</v>
+      </c>
+      <c r="O109" t="s">
+        <v>22</v>
+      </c>
+      <c r="P109" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -5785,24 +7079,36 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
-      </c>
-      <c r="J110" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K110" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+      <c r="N110" t="s">
+        <v>22</v>
+      </c>
+      <c r="O110" t="s">
+        <v>22</v>
+      </c>
+      <c r="P110" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5826,24 +7132,36 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
-      </c>
-      <c r="J111" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K111" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+      <c r="N111" t="s">
+        <v>22</v>
+      </c>
+      <c r="O111" t="s">
+        <v>22</v>
+      </c>
+      <c r="P111" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5867,24 +7185,36 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
-      </c>
-      <c r="J112" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K112" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+      <c r="N112" t="s">
+        <v>22</v>
+      </c>
+      <c r="O112" t="s">
+        <v>22</v>
+      </c>
+      <c r="P112" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5908,24 +7238,36 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
-      </c>
-      <c r="J113" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K113" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="N113" t="s">
+        <v>22</v>
+      </c>
+      <c r="O113" t="s">
+        <v>22</v>
+      </c>
+      <c r="P113" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5949,24 +7291,36 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
+        <v>29</v>
+      </c>
+      <c r="J114" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J114" t="s">
-        <v>15</v>
-      </c>
       <c r="K114" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+      <c r="N114" t="s">
+        <v>22</v>
+      </c>
+      <c r="O114" t="s">
+        <v>22</v>
+      </c>
+      <c r="P114" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -5990,24 +7344,36 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
-      </c>
-      <c r="J115" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K115" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="N115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O115" t="s">
+        <v>22</v>
+      </c>
+      <c r="P115" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6031,24 +7397,36 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
-      </c>
-      <c r="J116" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K116" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="N116" t="s">
+        <v>22</v>
+      </c>
+      <c r="O116" t="s">
+        <v>22</v>
+      </c>
+      <c r="P116" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6072,24 +7450,36 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
+        <v>29</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J117" t="s">
-        <v>15</v>
-      </c>
       <c r="K117" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+      <c r="N117" t="s">
+        <v>22</v>
+      </c>
+      <c r="O117" t="s">
+        <v>22</v>
+      </c>
+      <c r="P117" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6113,24 +7503,36 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
+        <v>29</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J118" t="s">
-        <v>15</v>
-      </c>
       <c r="K118" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+      <c r="N118" t="s">
+        <v>22</v>
+      </c>
+      <c r="O118" t="s">
+        <v>22</v>
+      </c>
+      <c r="P118" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6154,24 +7556,36 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K119" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+      <c r="N119" t="s">
+        <v>22</v>
+      </c>
+      <c r="O119" t="s">
+        <v>22</v>
+      </c>
+      <c r="P119" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6195,24 +7609,36 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
-      </c>
-      <c r="J120" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K120" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+      <c r="N120" t="s">
+        <v>22</v>
+      </c>
+      <c r="O120" t="s">
+        <v>22</v>
+      </c>
+      <c r="P120" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6236,24 +7662,36 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
-      </c>
-      <c r="J121" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K121" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+      <c r="N121" t="s">
+        <v>22</v>
+      </c>
+      <c r="O121" t="s">
+        <v>22</v>
+      </c>
+      <c r="P121" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6277,24 +7715,36 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
-      </c>
-      <c r="J122" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K122" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+      <c r="N122" t="s">
+        <v>22</v>
+      </c>
+      <c r="O122" t="s">
+        <v>22</v>
+      </c>
+      <c r="P122" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6318,24 +7768,36 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
-      </c>
-      <c r="J123" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K123" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+      <c r="N123" t="s">
+        <v>22</v>
+      </c>
+      <c r="O123" t="s">
+        <v>22</v>
+      </c>
+      <c r="P123" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6359,24 +7821,36 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
-      </c>
-      <c r="J124" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K124" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+      <c r="N124" t="s">
+        <v>22</v>
+      </c>
+      <c r="O124" t="s">
+        <v>22</v>
+      </c>
+      <c r="P124" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -6400,24 +7874,36 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
+        <v>29</v>
+      </c>
+      <c r="J125" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J125" t="s">
-        <v>15</v>
-      </c>
       <c r="K125" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+      <c r="N125" t="s">
+        <v>22</v>
+      </c>
+      <c r="O125" t="s">
+        <v>22</v>
+      </c>
+      <c r="P125" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -6441,24 +7927,36 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
-      </c>
-      <c r="J126" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K126" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+      <c r="N126" t="s">
+        <v>22</v>
+      </c>
+      <c r="O126" t="s">
+        <v>22</v>
+      </c>
+      <c r="P126" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -6482,24 +7980,36 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
-      </c>
-      <c r="J127" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K127" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+      <c r="N127" t="s">
+        <v>22</v>
+      </c>
+      <c r="O127" t="s">
+        <v>22</v>
+      </c>
+      <c r="P127" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -6523,24 +8033,36 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
-      </c>
-      <c r="J128" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K128" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="N128" t="s">
+        <v>22</v>
+      </c>
+      <c r="O128" t="s">
+        <v>22</v>
+      </c>
+      <c r="P128" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -6564,24 +8086,36 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
-      </c>
-      <c r="J129" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K129" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="N129" t="s">
+        <v>22</v>
+      </c>
+      <c r="O129" t="s">
+        <v>22</v>
+      </c>
+      <c r="P129" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -6605,24 +8139,36 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
+        <v>29</v>
+      </c>
+      <c r="J130" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J130" t="s">
-        <v>15</v>
-      </c>
       <c r="K130" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+      <c r="N130" t="s">
+        <v>22</v>
+      </c>
+      <c r="O130" t="s">
+        <v>22</v>
+      </c>
+      <c r="P130" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -6646,24 +8192,36 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
-      </c>
-      <c r="J131" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K131" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="N131" t="s">
+        <v>22</v>
+      </c>
+      <c r="O131" t="s">
+        <v>22</v>
+      </c>
+      <c r="P131" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -6687,24 +8245,36 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J132" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K132" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="N132" t="s">
+        <v>22</v>
+      </c>
+      <c r="O132" t="s">
+        <v>22</v>
+      </c>
+      <c r="P132" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -6728,24 +8298,36 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
+        <v>29</v>
+      </c>
+      <c r="J133" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J133" t="s">
-        <v>15</v>
-      </c>
       <c r="K133" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+      <c r="N133" t="s">
+        <v>22</v>
+      </c>
+      <c r="O133" t="s">
+        <v>22</v>
+      </c>
+      <c r="P133" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -6769,24 +8351,36 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
-      </c>
-      <c r="J134" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K134" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+        <v>229</v>
+      </c>
+      <c r="N134" t="s">
+        <v>22</v>
+      </c>
+      <c r="O134" t="s">
+        <v>22</v>
+      </c>
+      <c r="P134" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -6810,24 +8404,36 @@
         <v>0</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
-      </c>
-      <c r="J135" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K135" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="N135" t="s">
+        <v>22</v>
+      </c>
+      <c r="O135" t="s">
+        <v>22</v>
+      </c>
+      <c r="P135" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -6851,24 +8457,36 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
-      </c>
-      <c r="J136" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K136" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+      <c r="N136" t="s">
+        <v>22</v>
+      </c>
+      <c r="O136" t="s">
+        <v>22</v>
+      </c>
+      <c r="P136" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -6892,24 +8510,36 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
-      </c>
-      <c r="J137" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K137" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+        <v>235</v>
+      </c>
+      <c r="N137" t="s">
+        <v>22</v>
+      </c>
+      <c r="O137" t="s">
+        <v>22</v>
+      </c>
+      <c r="P137" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -6933,24 +8563,36 @@
         <v>0</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
-      </c>
-      <c r="J138" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K138" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="N138" t="s">
+        <v>22</v>
+      </c>
+      <c r="O138" t="s">
+        <v>22</v>
+      </c>
+      <c r="P138" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -6974,24 +8616,36 @@
         <v>0</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
-      </c>
-      <c r="J139" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+      <c r="N139" t="s">
+        <v>22</v>
+      </c>
+      <c r="O139" t="s">
+        <v>22</v>
+      </c>
+      <c r="P139" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -7015,24 +8669,36 @@
         <v>0</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
-      </c>
-      <c r="J140" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K140" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+      <c r="N140" t="s">
+        <v>22</v>
+      </c>
+      <c r="O140" t="s">
+        <v>22</v>
+      </c>
+      <c r="P140" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -7056,24 +8722,36 @@
         <v>0</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
-      </c>
-      <c r="J141" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K141" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+      <c r="N141" t="s">
+        <v>22</v>
+      </c>
+      <c r="O141" t="s">
+        <v>22</v>
+      </c>
+      <c r="P141" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -7097,24 +8775,36 @@
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
-      </c>
-      <c r="J142" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K142" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="N142" t="s">
+        <v>22</v>
+      </c>
+      <c r="O142" t="s">
+        <v>22</v>
+      </c>
+      <c r="P142" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -7138,24 +8828,36 @@
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
-      </c>
-      <c r="J143" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K143" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+      <c r="N143" t="s">
+        <v>22</v>
+      </c>
+      <c r="O143" t="s">
+        <v>22</v>
+      </c>
+      <c r="P143" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7179,24 +8881,36 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
-      </c>
-      <c r="J144" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K144" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="N144" t="s">
+        <v>22</v>
+      </c>
+      <c r="O144" t="s">
+        <v>22</v>
+      </c>
+      <c r="P144" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7220,24 +8934,36 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
-      </c>
-      <c r="J145" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K145" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+      <c r="N145" t="s">
+        <v>22</v>
+      </c>
+      <c r="O145" t="s">
+        <v>22</v>
+      </c>
+      <c r="P145" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7261,24 +8987,36 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
-      </c>
-      <c r="J146" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K146" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L146">
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="s">
+        <v>22</v>
+      </c>
+      <c r="P146" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7302,24 +9040,36 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
-      </c>
-      <c r="J147" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K147" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="s">
+        <v>22</v>
+      </c>
+      <c r="P147" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7343,24 +9093,36 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
-      </c>
-      <c r="J148" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="s">
+        <v>22</v>
+      </c>
+      <c r="P148" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7384,24 +9146,36 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
-      </c>
-      <c r="J149" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K149" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L149">
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+      <c r="N149" t="s">
+        <v>22</v>
+      </c>
+      <c r="O149" t="s">
+        <v>22</v>
+      </c>
+      <c r="P149" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7425,24 +9199,36 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>19</v>
-      </c>
-      <c r="J150" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K150" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+      <c r="N150" t="s">
+        <v>22</v>
+      </c>
+      <c r="O150" t="s">
+        <v>22</v>
+      </c>
+      <c r="P150" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7466,24 +9252,36 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
-      </c>
-      <c r="J151" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K151" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L151">
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="N151" t="s">
+        <v>22</v>
+      </c>
+      <c r="O151" t="s">
+        <v>22</v>
+      </c>
+      <c r="P151" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7507,24 +9305,36 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>19</v>
-      </c>
-      <c r="J152" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K152" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+      <c r="N152" t="s">
+        <v>22</v>
+      </c>
+      <c r="O152" t="s">
+        <v>22</v>
+      </c>
+      <c r="P152" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7548,24 +9358,36 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
-      </c>
-      <c r="J153" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K153" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+      <c r="N153" t="s">
+        <v>22</v>
+      </c>
+      <c r="O153" t="s">
+        <v>22</v>
+      </c>
+      <c r="P153" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7589,24 +9411,36 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
+        <v>29</v>
+      </c>
+      <c r="J154" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J154" t="s">
-        <v>20</v>
-      </c>
       <c r="K154" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L154">
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+      <c r="N154" t="s">
+        <v>22</v>
+      </c>
+      <c r="O154" t="s">
+        <v>22</v>
+      </c>
+      <c r="P154" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7630,24 +9464,36 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
-      </c>
-      <c r="J155" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K155" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+      <c r="N155" t="s">
+        <v>22</v>
+      </c>
+      <c r="O155" t="s">
+        <v>22</v>
+      </c>
+      <c r="P155" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7671,24 +9517,36 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
-      </c>
-      <c r="J156" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+      <c r="N156" t="s">
+        <v>22</v>
+      </c>
+      <c r="O156" t="s">
+        <v>22</v>
+      </c>
+      <c r="P156" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7712,24 +9570,36 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
+        <v>29</v>
+      </c>
+      <c r="J157" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J157" t="s">
-        <v>15</v>
-      </c>
       <c r="K157" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+      <c r="N157" t="s">
+        <v>22</v>
+      </c>
+      <c r="O157" t="s">
+        <v>22</v>
+      </c>
+      <c r="P157" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7753,24 +9623,36 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
-      </c>
-      <c r="J158" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K158" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L158">
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="s">
+        <v>22</v>
+      </c>
+      <c r="P158" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -7794,24 +9676,36 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
+        <v>29</v>
+      </c>
+      <c r="J159" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J159" t="s">
-        <v>15</v>
-      </c>
       <c r="K159" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L159">
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="s">
+        <v>22</v>
+      </c>
+      <c r="P159" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7835,24 +9729,36 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
-      </c>
-      <c r="J160" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K160" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L160">
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="s">
+        <v>22</v>
+      </c>
+      <c r="P160" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -7876,24 +9782,36 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>19</v>
-      </c>
-      <c r="J161" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K161" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L161">
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+      <c r="N161" t="s">
+        <v>22</v>
+      </c>
+      <c r="O161" t="s">
+        <v>22</v>
+      </c>
+      <c r="P161" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -7917,24 +9835,36 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
-      </c>
-      <c r="J162" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K162" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L162">
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+      <c r="N162" t="s">
+        <v>22</v>
+      </c>
+      <c r="O162" t="s">
+        <v>22</v>
+      </c>
+      <c r="P162" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -7958,24 +9888,36 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>19</v>
-      </c>
-      <c r="J163" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K163" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L163">
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+      <c r="N163" t="s">
+        <v>22</v>
+      </c>
+      <c r="O163" t="s">
+        <v>22</v>
+      </c>
+      <c r="P163" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -7999,24 +9941,36 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>19</v>
-      </c>
-      <c r="J164" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K164" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+      <c r="N164" t="s">
+        <v>22</v>
+      </c>
+      <c r="O164" t="s">
+        <v>22</v>
+      </c>
+      <c r="P164" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -8040,25 +9994,37 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>19</v>
-      </c>
-      <c r="J165" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K165" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L165">
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>285</v>
+        <v>291</v>
+      </c>
+      <c r="N165" t="s">
+        <v>22</v>
+      </c>
+      <c r="O165" t="s">
+        <v>22</v>
+      </c>
+      <c r="P165" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M54 A56:M83 B55:M55 A85:M165 B84:M84" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q1 A2:I165 K2:Q165" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2C67CB-58A8-4CE1-91A3-207DAC58AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70671D8-D42B-4A3C-A7AD-60F89E1B5E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
@@ -247,9 +247,6 @@
     <t>Copenhagen Wolves</t>
   </si>
   <si>
-    <t>Counter Logic Games</t>
-  </si>
-  <si>
     <t>ENCE Academy</t>
   </si>
   <si>
@@ -896,6 +893,9 @@
   </si>
   <si>
     <t>2026-02-19T01:45:20.251Z</t>
+  </si>
+  <si>
+    <t>Counter Logic</t>
   </si>
 </sst>
 </file>
@@ -931,8 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1275,6 +1274,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q165"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1357,7 +1359,7 @@
       <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" t="s">
@@ -1410,7 +1412,7 @@
       <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>24</v>
       </c>
       <c r="K3" t="s">
@@ -1463,7 +1465,7 @@
       <c r="I4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
@@ -1516,7 +1518,7 @@
       <c r="I5" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>24</v>
       </c>
       <c r="K5" t="s">
@@ -1569,7 +1571,7 @@
       <c r="I6" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>32</v>
       </c>
       <c r="K6" t="s">
@@ -1622,7 +1624,7 @@
       <c r="I7" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>32</v>
       </c>
       <c r="K7" t="s">
@@ -1675,7 +1677,7 @@
       <c r="I8" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>24</v>
       </c>
       <c r="K8" t="s">
@@ -1728,7 +1730,7 @@
       <c r="I9" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>32</v>
       </c>
       <c r="K9" t="s">
@@ -1781,7 +1783,7 @@
       <c r="I10" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>32</v>
       </c>
       <c r="K10" t="s">
@@ -1834,7 +1836,7 @@
       <c r="I11" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>32</v>
       </c>
       <c r="K11" t="s">
@@ -1887,7 +1889,7 @@
       <c r="I12" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>32</v>
       </c>
       <c r="K12" t="s">
@@ -1940,7 +1942,7 @@
       <c r="I13" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>32</v>
       </c>
       <c r="K13" t="s">
@@ -1993,7 +1995,7 @@
       <c r="I14" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>19</v>
       </c>
       <c r="K14" t="s">
@@ -2046,7 +2048,7 @@
       <c r="I15" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>32</v>
       </c>
       <c r="K15" t="s">
@@ -2099,7 +2101,7 @@
       <c r="I16" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>32</v>
       </c>
       <c r="K16" t="s">
@@ -2152,7 +2154,7 @@
       <c r="I17" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>32</v>
       </c>
       <c r="K17" t="s">
@@ -2205,7 +2207,7 @@
       <c r="I18" t="s">
         <v>29</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>32</v>
       </c>
       <c r="K18" t="s">
@@ -2258,7 +2260,7 @@
       <c r="I19" t="s">
         <v>29</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>24</v>
       </c>
       <c r="K19" t="s">
@@ -2311,7 +2313,7 @@
       <c r="I20" t="s">
         <v>29</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>24</v>
       </c>
       <c r="K20" t="s">
@@ -2364,7 +2366,7 @@
       <c r="I21" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>19</v>
       </c>
       <c r="K21" t="s">
@@ -2417,7 +2419,7 @@
       <c r="I22" t="s">
         <v>29</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>32</v>
       </c>
       <c r="K22" t="s">
@@ -2470,7 +2472,7 @@
       <c r="I23" t="s">
         <v>29</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>24</v>
       </c>
       <c r="K23" t="s">
@@ -2523,7 +2525,7 @@
       <c r="I24" t="s">
         <v>29</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>32</v>
       </c>
       <c r="K24" t="s">
@@ -2576,7 +2578,7 @@
       <c r="I25" t="s">
         <v>29</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>32</v>
       </c>
       <c r="K25" t="s">
@@ -2629,7 +2631,7 @@
       <c r="I26" t="s">
         <v>29</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>32</v>
       </c>
       <c r="K26" t="s">
@@ -2682,7 +2684,7 @@
       <c r="I27" t="s">
         <v>29</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>32</v>
       </c>
       <c r="K27" t="s">
@@ -2735,7 +2737,7 @@
       <c r="I28" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>24</v>
       </c>
       <c r="K28" t="s">
@@ -2788,7 +2790,7 @@
       <c r="I29" t="s">
         <v>29</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>24</v>
       </c>
       <c r="K29" t="s">
@@ -2841,7 +2843,7 @@
       <c r="I30" t="s">
         <v>29</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>32</v>
       </c>
       <c r="K30" t="s">
@@ -2894,7 +2896,7 @@
       <c r="I31" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>32</v>
       </c>
       <c r="K31" t="s">
@@ -2947,7 +2949,7 @@
       <c r="I32" t="s">
         <v>29</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>19</v>
       </c>
       <c r="K32" t="s">
@@ -3000,7 +3002,7 @@
       <c r="I33" t="s">
         <v>29</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>24</v>
       </c>
       <c r="K33" t="s">
@@ -3053,7 +3055,7 @@
       <c r="I34" t="s">
         <v>29</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>32</v>
       </c>
       <c r="K34" t="s">
@@ -3106,7 +3108,7 @@
       <c r="I35" t="s">
         <v>29</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>19</v>
       </c>
       <c r="K35" t="s">
@@ -3159,7 +3161,7 @@
       <c r="I36" t="s">
         <v>29</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>32</v>
       </c>
       <c r="K36" t="s">
@@ -3186,7 +3188,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3212,7 +3214,7 @@
       <c r="I37" t="s">
         <v>29</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>24</v>
       </c>
       <c r="K37" t="s">
@@ -3239,7 +3241,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3265,7 +3267,7 @@
       <c r="I38" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>32</v>
       </c>
       <c r="K38" t="s">
@@ -3292,7 +3294,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3318,7 +3320,7 @@
       <c r="I39" t="s">
         <v>29</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>32</v>
       </c>
       <c r="K39" t="s">
@@ -3345,7 +3347,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3371,7 +3373,7 @@
       <c r="I40" t="s">
         <v>29</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>32</v>
       </c>
       <c r="K40" t="s">
@@ -3398,7 +3400,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3424,7 +3426,7 @@
       <c r="I41" t="s">
         <v>29</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>32</v>
       </c>
       <c r="K41" t="s">
@@ -3451,7 +3453,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3477,7 +3479,7 @@
       <c r="I42" t="s">
         <v>29</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>32</v>
       </c>
       <c r="K42" t="s">
@@ -3504,7 +3506,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3530,7 +3532,7 @@
       <c r="I43" t="s">
         <v>29</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>32</v>
       </c>
       <c r="K43" t="s">
@@ -3557,7 +3559,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3583,7 +3585,7 @@
       <c r="I44" t="s">
         <v>29</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" t="s">
         <v>19</v>
       </c>
       <c r="K44" t="s">
@@ -3610,7 +3612,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3636,7 +3638,7 @@
       <c r="I45" t="s">
         <v>29</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>32</v>
       </c>
       <c r="K45" t="s">
@@ -3663,7 +3665,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3689,7 +3691,7 @@
       <c r="I46" t="s">
         <v>29</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>19</v>
       </c>
       <c r="K46" t="s">
@@ -3716,7 +3718,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3742,7 +3744,7 @@
       <c r="I47" t="s">
         <v>29</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" t="s">
         <v>32</v>
       </c>
       <c r="K47" t="s">
@@ -3769,7 +3771,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3795,7 +3797,7 @@
       <c r="I48" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>32</v>
       </c>
       <c r="K48" t="s">
@@ -3822,7 +3824,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3848,7 +3850,7 @@
       <c r="I49" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>32</v>
       </c>
       <c r="K49" t="s">
@@ -3875,7 +3877,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3901,7 +3903,7 @@
       <c r="I50" t="s">
         <v>29</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>32</v>
       </c>
       <c r="K50" t="s">
@@ -3928,7 +3930,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3954,7 +3956,7 @@
       <c r="I51" t="s">
         <v>29</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" t="s">
         <v>24</v>
       </c>
       <c r="K51" t="s">
@@ -3981,7 +3983,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4007,7 +4009,7 @@
       <c r="I52" t="s">
         <v>29</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>24</v>
       </c>
       <c r="K52" t="s">
@@ -4034,7 +4036,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4060,7 +4062,7 @@
       <c r="I53" t="s">
         <v>29</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" t="s">
         <v>32</v>
       </c>
       <c r="K53" t="s">
@@ -4087,7 +4089,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4113,7 +4115,7 @@
       <c r="I54" t="s">
         <v>29</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>19</v>
       </c>
       <c r="K54" t="s">
@@ -4140,7 +4142,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -4166,7 +4168,7 @@
       <c r="I55" t="s">
         <v>29</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" t="s">
         <v>19</v>
       </c>
       <c r="K55" t="s">
@@ -4193,7 +4195,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4219,7 +4221,7 @@
       <c r="I56" t="s">
         <v>29</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>32</v>
       </c>
       <c r="K56" t="s">
@@ -4246,7 +4248,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -4272,7 +4274,7 @@
       <c r="I57" t="s">
         <v>29</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>24</v>
       </c>
       <c r="K57" t="s">
@@ -4299,7 +4301,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -4325,7 +4327,7 @@
       <c r="I58" t="s">
         <v>29</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>24</v>
       </c>
       <c r="K58" t="s">
@@ -4352,7 +4354,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -4378,7 +4380,7 @@
       <c r="I59" t="s">
         <v>29</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>32</v>
       </c>
       <c r="K59" t="s">
@@ -4405,7 +4407,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -4431,7 +4433,7 @@
       <c r="I60" t="s">
         <v>29</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>32</v>
       </c>
       <c r="K60" t="s">
@@ -4458,7 +4460,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4484,7 +4486,7 @@
       <c r="I61" t="s">
         <v>29</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" t="s">
         <v>32</v>
       </c>
       <c r="K61" t="s">
@@ -4511,7 +4513,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -4537,7 +4539,7 @@
       <c r="I62" t="s">
         <v>29</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" t="s">
         <v>32</v>
       </c>
       <c r="K62" t="s">
@@ -4564,7 +4566,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -4590,7 +4592,7 @@
       <c r="I63" t="s">
         <v>29</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" t="s">
         <v>32</v>
       </c>
       <c r="K63" t="s">
@@ -4617,7 +4619,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -4643,7 +4645,7 @@
       <c r="I64" t="s">
         <v>29</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" t="s">
         <v>32</v>
       </c>
       <c r="K64" t="s">
@@ -4670,7 +4672,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -4696,7 +4698,7 @@
       <c r="I65" t="s">
         <v>29</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" t="s">
         <v>32</v>
       </c>
       <c r="K65" t="s">
@@ -4723,7 +4725,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -4749,7 +4751,7 @@
       <c r="I66" t="s">
         <v>29</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" t="s">
         <v>24</v>
       </c>
       <c r="K66" t="s">
@@ -4776,7 +4778,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -4802,7 +4804,7 @@
       <c r="I67" t="s">
         <v>29</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" t="s">
         <v>32</v>
       </c>
       <c r="K67" t="s">
@@ -4829,7 +4831,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -4855,7 +4857,7 @@
       <c r="I68" t="s">
         <v>29</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" t="s">
         <v>32</v>
       </c>
       <c r="K68" t="s">
@@ -4882,7 +4884,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4908,7 +4910,7 @@
       <c r="I69" t="s">
         <v>29</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" t="s">
         <v>19</v>
       </c>
       <c r="K69" t="s">
@@ -4935,7 +4937,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4961,7 +4963,7 @@
       <c r="I70" t="s">
         <v>29</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" t="s">
         <v>19</v>
       </c>
       <c r="K70" t="s">
@@ -4988,7 +4990,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -5014,7 +5016,7 @@
       <c r="I71" t="s">
         <v>29</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" t="s">
         <v>32</v>
       </c>
       <c r="K71" t="s">
@@ -5041,7 +5043,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -5067,7 +5069,7 @@
       <c r="I72" t="s">
         <v>29</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" t="s">
         <v>32</v>
       </c>
       <c r="K72" t="s">
@@ -5094,7 +5096,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -5120,7 +5122,7 @@
       <c r="I73" t="s">
         <v>29</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" t="s">
         <v>24</v>
       </c>
       <c r="K73" t="s">
@@ -5147,7 +5149,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -5173,7 +5175,7 @@
       <c r="I74" t="s">
         <v>29</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" t="s">
         <v>32</v>
       </c>
       <c r="K74" t="s">
@@ -5200,7 +5202,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -5226,7 +5228,7 @@
       <c r="I75" t="s">
         <v>29</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" t="s">
         <v>32</v>
       </c>
       <c r="K75" t="s">
@@ -5253,7 +5255,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -5279,7 +5281,7 @@
       <c r="I76" t="s">
         <v>29</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" t="s">
         <v>32</v>
       </c>
       <c r="K76" t="s">
@@ -5306,7 +5308,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -5332,7 +5334,7 @@
       <c r="I77" t="s">
         <v>29</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" t="s">
         <v>32</v>
       </c>
       <c r="K77" t="s">
@@ -5359,7 +5361,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -5385,7 +5387,7 @@
       <c r="I78" t="s">
         <v>29</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" t="s">
         <v>19</v>
       </c>
       <c r="K78" t="s">
@@ -5395,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N78" t="s">
         <v>22</v>
@@ -5412,7 +5414,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -5438,7 +5440,7 @@
       <c r="I79" t="s">
         <v>29</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" t="s">
         <v>32</v>
       </c>
       <c r="K79" t="s">
@@ -5448,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N79" t="s">
         <v>22</v>
@@ -5465,7 +5467,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -5491,7 +5493,7 @@
       <c r="I80" t="s">
         <v>29</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" t="s">
         <v>32</v>
       </c>
       <c r="K80" t="s">
@@ -5501,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N80" t="s">
         <v>22</v>
@@ -5518,7 +5520,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -5544,7 +5546,7 @@
       <c r="I81" t="s">
         <v>29</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" t="s">
         <v>32</v>
       </c>
       <c r="K81" t="s">
@@ -5554,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N81" t="s">
         <v>22</v>
@@ -5571,7 +5573,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -5597,7 +5599,7 @@
       <c r="I82" t="s">
         <v>29</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" t="s">
         <v>24</v>
       </c>
       <c r="K82" t="s">
@@ -5607,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N82" t="s">
         <v>22</v>
@@ -5624,7 +5626,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -5650,7 +5652,7 @@
       <c r="I83" t="s">
         <v>29</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="J83" t="s">
         <v>24</v>
       </c>
       <c r="K83" t="s">
@@ -5660,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N83" t="s">
         <v>22</v>
@@ -5677,7 +5679,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -5703,7 +5705,7 @@
       <c r="I84" t="s">
         <v>29</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" t="s">
         <v>19</v>
       </c>
       <c r="K84" t="s">
@@ -5713,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N84" t="s">
         <v>22</v>
@@ -5730,7 +5732,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -5756,7 +5758,7 @@
       <c r="I85" t="s">
         <v>29</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" t="s">
         <v>32</v>
       </c>
       <c r="K85" t="s">
@@ -5766,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N85" t="s">
         <v>22</v>
@@ -5783,7 +5785,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -5809,7 +5811,7 @@
       <c r="I86" t="s">
         <v>29</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" t="s">
         <v>32</v>
       </c>
       <c r="K86" t="s">
@@ -5819,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N86" t="s">
         <v>22</v>
@@ -5836,7 +5838,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -5862,7 +5864,7 @@
       <c r="I87" t="s">
         <v>29</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" t="s">
         <v>24</v>
       </c>
       <c r="K87" t="s">
@@ -5872,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N87" t="s">
         <v>22</v>
@@ -5889,7 +5891,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5915,7 +5917,7 @@
       <c r="I88" t="s">
         <v>29</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="J88" t="s">
         <v>32</v>
       </c>
       <c r="K88" t="s">
@@ -5925,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N88" t="s">
         <v>22</v>
@@ -5942,7 +5944,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5968,7 +5970,7 @@
       <c r="I89" t="s">
         <v>29</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="J89" t="s">
         <v>24</v>
       </c>
       <c r="K89" t="s">
@@ -5978,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N89" t="s">
         <v>22</v>
@@ -5995,7 +5997,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -6021,7 +6023,7 @@
       <c r="I90" t="s">
         <v>29</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="J90" t="s">
         <v>32</v>
       </c>
       <c r="K90" t="s">
@@ -6031,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N90" t="s">
         <v>22</v>
@@ -6048,7 +6050,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -6074,7 +6076,7 @@
       <c r="I91" t="s">
         <v>29</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="J91" t="s">
         <v>32</v>
       </c>
       <c r="K91" t="s">
@@ -6084,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N91" t="s">
         <v>22</v>
@@ -6101,7 +6103,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -6127,7 +6129,7 @@
       <c r="I92" t="s">
         <v>29</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J92" t="s">
         <v>24</v>
       </c>
       <c r="K92" t="s">
@@ -6137,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N92" t="s">
         <v>22</v>
@@ -6154,7 +6156,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -6180,7 +6182,7 @@
       <c r="I93" t="s">
         <v>29</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="J93" t="s">
         <v>24</v>
       </c>
       <c r="K93" t="s">
@@ -6190,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N93" t="s">
         <v>22</v>
@@ -6207,7 +6209,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -6233,7 +6235,7 @@
       <c r="I94" t="s">
         <v>29</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="J94" t="s">
         <v>24</v>
       </c>
       <c r="K94" t="s">
@@ -6243,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N94" t="s">
         <v>22</v>
@@ -6260,7 +6262,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -6286,7 +6288,7 @@
       <c r="I95" t="s">
         <v>29</v>
       </c>
-      <c r="J95" s="1" t="s">
+      <c r="J95" t="s">
         <v>32</v>
       </c>
       <c r="K95" t="s">
@@ -6296,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N95" t="s">
         <v>22</v>
@@ -6313,7 +6315,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -6339,7 +6341,7 @@
       <c r="I96" t="s">
         <v>29</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="J96" t="s">
         <v>24</v>
       </c>
       <c r="K96" t="s">
@@ -6349,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N96" t="s">
         <v>22</v>
@@ -6366,7 +6368,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -6392,7 +6394,7 @@
       <c r="I97" t="s">
         <v>29</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="J97" t="s">
         <v>19</v>
       </c>
       <c r="K97" t="s">
@@ -6402,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N97" t="s">
         <v>22</v>
@@ -6419,7 +6421,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -6445,7 +6447,7 @@
       <c r="I98" t="s">
         <v>29</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="J98" t="s">
         <v>32</v>
       </c>
       <c r="K98" t="s">
@@ -6455,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N98" t="s">
         <v>22</v>
@@ -6472,7 +6474,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -6498,7 +6500,7 @@
       <c r="I99" t="s">
         <v>29</v>
       </c>
-      <c r="J99" s="1" t="s">
+      <c r="J99" t="s">
         <v>19</v>
       </c>
       <c r="K99" t="s">
@@ -6508,7 +6510,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N99" t="s">
         <v>22</v>
@@ -6525,7 +6527,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -6551,7 +6553,7 @@
       <c r="I100" t="s">
         <v>29</v>
       </c>
-      <c r="J100" s="1" t="s">
+      <c r="J100" t="s">
         <v>32</v>
       </c>
       <c r="K100" t="s">
@@ -6561,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N100" t="s">
         <v>22</v>
@@ -6578,7 +6580,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -6604,7 +6606,7 @@
       <c r="I101" t="s">
         <v>29</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="J101" t="s">
         <v>24</v>
       </c>
       <c r="K101" t="s">
@@ -6614,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N101" t="s">
         <v>22</v>
@@ -6631,7 +6633,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -6657,7 +6659,7 @@
       <c r="I102" t="s">
         <v>29</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" t="s">
         <v>32</v>
       </c>
       <c r="K102" t="s">
@@ -6667,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N102" t="s">
         <v>22</v>
@@ -6684,7 +6686,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -6710,7 +6712,7 @@
       <c r="I103" t="s">
         <v>29</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="J103" t="s">
         <v>19</v>
       </c>
       <c r="K103" t="s">
@@ -6720,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N103" t="s">
         <v>22</v>
@@ -6737,7 +6739,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -6763,7 +6765,7 @@
       <c r="I104" t="s">
         <v>29</v>
       </c>
-      <c r="J104" s="1" t="s">
+      <c r="J104" t="s">
         <v>24</v>
       </c>
       <c r="K104" t="s">
@@ -6773,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N104" t="s">
         <v>22</v>
@@ -6790,7 +6792,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -6816,7 +6818,7 @@
       <c r="I105" t="s">
         <v>29</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="J105" t="s">
         <v>32</v>
       </c>
       <c r="K105" t="s">
@@ -6826,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N105" t="s">
         <v>22</v>
@@ -6843,7 +6845,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6869,7 +6871,7 @@
       <c r="I106" t="s">
         <v>29</v>
       </c>
-      <c r="J106" s="1" t="s">
+      <c r="J106" t="s">
         <v>32</v>
       </c>
       <c r="K106" t="s">
@@ -6879,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N106" t="s">
         <v>22</v>
@@ -6896,7 +6898,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6922,7 +6924,7 @@
       <c r="I107" t="s">
         <v>29</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="J107" t="s">
         <v>32</v>
       </c>
       <c r="K107" t="s">
@@ -6932,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N107" t="s">
         <v>22</v>
@@ -6949,7 +6951,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6975,7 +6977,7 @@
       <c r="I108" t="s">
         <v>29</v>
       </c>
-      <c r="J108" s="1" t="s">
+      <c r="J108" t="s">
         <v>32</v>
       </c>
       <c r="K108" t="s">
@@ -6985,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N108" t="s">
         <v>22</v>
@@ -7002,7 +7004,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -7028,7 +7030,7 @@
       <c r="I109" t="s">
         <v>29</v>
       </c>
-      <c r="J109" s="1" t="s">
+      <c r="J109" t="s">
         <v>32</v>
       </c>
       <c r="K109" t="s">
@@ -7038,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N109" t="s">
         <v>22</v>
@@ -7055,7 +7057,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -7081,7 +7083,7 @@
       <c r="I110" t="s">
         <v>29</v>
       </c>
-      <c r="J110" s="1" t="s">
+      <c r="J110" t="s">
         <v>32</v>
       </c>
       <c r="K110" t="s">
@@ -7091,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N110" t="s">
         <v>22</v>
@@ -7108,7 +7110,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -7134,7 +7136,7 @@
       <c r="I111" t="s">
         <v>29</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="J111" t="s">
         <v>32</v>
       </c>
       <c r="K111" t="s">
@@ -7144,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N111" t="s">
         <v>22</v>
@@ -7161,7 +7163,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -7187,7 +7189,7 @@
       <c r="I112" t="s">
         <v>29</v>
       </c>
-      <c r="J112" s="1" t="s">
+      <c r="J112" t="s">
         <v>32</v>
       </c>
       <c r="K112" t="s">
@@ -7197,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N112" t="s">
         <v>22</v>
@@ -7214,7 +7216,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -7240,7 +7242,7 @@
       <c r="I113" t="s">
         <v>29</v>
       </c>
-      <c r="J113" s="1" t="s">
+      <c r="J113" t="s">
         <v>32</v>
       </c>
       <c r="K113" t="s">
@@ -7250,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N113" t="s">
         <v>22</v>
@@ -7267,7 +7269,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -7293,7 +7295,7 @@
       <c r="I114" t="s">
         <v>29</v>
       </c>
-      <c r="J114" s="1" t="s">
+      <c r="J114" t="s">
         <v>19</v>
       </c>
       <c r="K114" t="s">
@@ -7303,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N114" t="s">
         <v>22</v>
@@ -7320,7 +7322,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -7346,7 +7348,7 @@
       <c r="I115" t="s">
         <v>29</v>
       </c>
-      <c r="J115" s="1" t="s">
+      <c r="J115" t="s">
         <v>32</v>
       </c>
       <c r="K115" t="s">
@@ -7356,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N115" t="s">
         <v>22</v>
@@ -7373,7 +7375,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -7399,7 +7401,7 @@
       <c r="I116" t="s">
         <v>29</v>
       </c>
-      <c r="J116" s="1" t="s">
+      <c r="J116" t="s">
         <v>32</v>
       </c>
       <c r="K116" t="s">
@@ -7409,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N116" t="s">
         <v>22</v>
@@ -7426,7 +7428,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -7452,7 +7454,7 @@
       <c r="I117" t="s">
         <v>29</v>
       </c>
-      <c r="J117" s="1" t="s">
+      <c r="J117" t="s">
         <v>19</v>
       </c>
       <c r="K117" t="s">
@@ -7462,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N117" t="s">
         <v>22</v>
@@ -7479,7 +7481,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -7505,7 +7507,7 @@
       <c r="I118" t="s">
         <v>29</v>
       </c>
-      <c r="J118" s="1" t="s">
+      <c r="J118" t="s">
         <v>19</v>
       </c>
       <c r="K118" t="s">
@@ -7515,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N118" t="s">
         <v>22</v>
@@ -7532,7 +7534,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -7558,7 +7560,7 @@
       <c r="I119" t="s">
         <v>29</v>
       </c>
-      <c r="J119" s="1" t="s">
+      <c r="J119" t="s">
         <v>32</v>
       </c>
       <c r="K119" t="s">
@@ -7568,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N119" t="s">
         <v>22</v>
@@ -7585,7 +7587,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -7611,7 +7613,7 @@
       <c r="I120" t="s">
         <v>29</v>
       </c>
-      <c r="J120" s="1" t="s">
+      <c r="J120" t="s">
         <v>32</v>
       </c>
       <c r="K120" t="s">
@@ -7621,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N120" t="s">
         <v>22</v>
@@ -7638,7 +7640,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -7664,7 +7666,7 @@
       <c r="I121" t="s">
         <v>29</v>
       </c>
-      <c r="J121" s="1" t="s">
+      <c r="J121" t="s">
         <v>24</v>
       </c>
       <c r="K121" t="s">
@@ -7674,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N121" t="s">
         <v>22</v>
@@ -7691,7 +7693,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -7717,7 +7719,7 @@
       <c r="I122" t="s">
         <v>29</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="J122" t="s">
         <v>32</v>
       </c>
       <c r="K122" t="s">
@@ -7727,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
@@ -7744,7 +7746,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -7770,7 +7772,7 @@
       <c r="I123" t="s">
         <v>29</v>
       </c>
-      <c r="J123" s="1" t="s">
+      <c r="J123" t="s">
         <v>24</v>
       </c>
       <c r="K123" t="s">
@@ -7780,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
@@ -7797,7 +7799,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -7823,7 +7825,7 @@
       <c r="I124" t="s">
         <v>29</v>
       </c>
-      <c r="J124" s="1" t="s">
+      <c r="J124" t="s">
         <v>32</v>
       </c>
       <c r="K124" t="s">
@@ -7833,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
@@ -7850,7 +7852,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7876,7 +7878,7 @@
       <c r="I125" t="s">
         <v>29</v>
       </c>
-      <c r="J125" s="1" t="s">
+      <c r="J125" t="s">
         <v>19</v>
       </c>
       <c r="K125" t="s">
@@ -7886,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N125" t="s">
         <v>22</v>
@@ -7903,7 +7905,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7929,7 +7931,7 @@
       <c r="I126" t="s">
         <v>29</v>
       </c>
-      <c r="J126" s="1" t="s">
+      <c r="J126" t="s">
         <v>32</v>
       </c>
       <c r="K126" t="s">
@@ -7939,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N126" t="s">
         <v>22</v>
@@ -7956,7 +7958,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7982,7 +7984,7 @@
       <c r="I127" t="s">
         <v>29</v>
       </c>
-      <c r="J127" s="1" t="s">
+      <c r="J127" t="s">
         <v>32</v>
       </c>
       <c r="K127" t="s">
@@ -7992,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N127" t="s">
         <v>22</v>
@@ -8009,7 +8011,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8035,7 +8037,7 @@
       <c r="I128" t="s">
         <v>29</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="J128" t="s">
         <v>32</v>
       </c>
       <c r="K128" t="s">
@@ -8045,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N128" t="s">
         <v>22</v>
@@ -8062,7 +8064,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8088,7 +8090,7 @@
       <c r="I129" t="s">
         <v>29</v>
       </c>
-      <c r="J129" s="1" t="s">
+      <c r="J129" t="s">
         <v>24</v>
       </c>
       <c r="K129" t="s">
@@ -8098,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N129" t="s">
         <v>22</v>
@@ -8115,7 +8117,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8141,7 +8143,7 @@
       <c r="I130" t="s">
         <v>29</v>
       </c>
-      <c r="J130" s="1" t="s">
+      <c r="J130" t="s">
         <v>19</v>
       </c>
       <c r="K130" t="s">
@@ -8151,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N130" t="s">
         <v>22</v>
@@ -8168,7 +8170,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8194,7 +8196,7 @@
       <c r="I131" t="s">
         <v>29</v>
       </c>
-      <c r="J131" s="1" t="s">
+      <c r="J131" t="s">
         <v>32</v>
       </c>
       <c r="K131" t="s">
@@ -8204,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N131" t="s">
         <v>22</v>
@@ -8221,7 +8223,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8247,7 +8249,7 @@
       <c r="I132" t="s">
         <v>29</v>
       </c>
-      <c r="J132" s="1" t="s">
+      <c r="J132" t="s">
         <v>24</v>
       </c>
       <c r="K132" t="s">
@@ -8257,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N132" t="s">
         <v>22</v>
@@ -8274,7 +8276,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8300,7 +8302,7 @@
       <c r="I133" t="s">
         <v>29</v>
       </c>
-      <c r="J133" s="1" t="s">
+      <c r="J133" t="s">
         <v>19</v>
       </c>
       <c r="K133" t="s">
@@ -8310,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N133" t="s">
         <v>22</v>
@@ -8327,7 +8329,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8353,7 +8355,7 @@
       <c r="I134" t="s">
         <v>29</v>
       </c>
-      <c r="J134" s="1" t="s">
+      <c r="J134" t="s">
         <v>32</v>
       </c>
       <c r="K134" t="s">
@@ -8363,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
@@ -8380,7 +8382,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8406,7 +8408,7 @@
       <c r="I135" t="s">
         <v>29</v>
       </c>
-      <c r="J135" s="1" t="s">
+      <c r="J135" t="s">
         <v>24</v>
       </c>
       <c r="K135" t="s">
@@ -8416,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
@@ -8433,7 +8435,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8459,7 +8461,7 @@
       <c r="I136" t="s">
         <v>29</v>
       </c>
-      <c r="J136" s="1" t="s">
+      <c r="J136" t="s">
         <v>32</v>
       </c>
       <c r="K136" t="s">
@@ -8469,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
@@ -8486,7 +8488,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8512,7 +8514,7 @@
       <c r="I137" t="s">
         <v>29</v>
       </c>
-      <c r="J137" s="1" t="s">
+      <c r="J137" t="s">
         <v>24</v>
       </c>
       <c r="K137" t="s">
@@ -8522,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N137" t="s">
         <v>22</v>
@@ -8539,7 +8541,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8565,7 +8567,7 @@
       <c r="I138" t="s">
         <v>29</v>
       </c>
-      <c r="J138" s="1" t="s">
+      <c r="J138" t="s">
         <v>32</v>
       </c>
       <c r="K138" t="s">
@@ -8575,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N138" t="s">
         <v>22</v>
@@ -8592,7 +8594,7 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8618,7 +8620,7 @@
       <c r="I139" t="s">
         <v>29</v>
       </c>
-      <c r="J139" s="1" t="s">
+      <c r="J139" t="s">
         <v>24</v>
       </c>
       <c r="K139" t="s">
@@ -8628,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N139" t="s">
         <v>22</v>
@@ -8645,7 +8647,7 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8671,7 +8673,7 @@
       <c r="I140" t="s">
         <v>29</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J140" t="s">
         <v>24</v>
       </c>
       <c r="K140" t="s">
@@ -8681,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N140" t="s">
         <v>22</v>
@@ -8698,7 +8700,7 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8724,7 +8726,7 @@
       <c r="I141" t="s">
         <v>29</v>
       </c>
-      <c r="J141" s="1" t="s">
+      <c r="J141" t="s">
         <v>24</v>
       </c>
       <c r="K141" t="s">
@@ -8734,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N141" t="s">
         <v>22</v>
@@ -8751,7 +8753,7 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8777,7 +8779,7 @@
       <c r="I142" t="s">
         <v>29</v>
       </c>
-      <c r="J142" s="1" t="s">
+      <c r="J142" t="s">
         <v>24</v>
       </c>
       <c r="K142" t="s">
@@ -8787,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N142" t="s">
         <v>22</v>
@@ -8804,7 +8806,7 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8830,7 +8832,7 @@
       <c r="I143" t="s">
         <v>29</v>
       </c>
-      <c r="J143" s="1" t="s">
+      <c r="J143" t="s">
         <v>32</v>
       </c>
       <c r="K143" t="s">
@@ -8840,7 +8842,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N143" t="s">
         <v>22</v>
@@ -8857,7 +8859,7 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8883,7 +8885,7 @@
       <c r="I144" t="s">
         <v>29</v>
       </c>
-      <c r="J144" s="1" t="s">
+      <c r="J144" t="s">
         <v>32</v>
       </c>
       <c r="K144" t="s">
@@ -8893,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N144" t="s">
         <v>22</v>
@@ -8910,7 +8912,7 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8936,7 +8938,7 @@
       <c r="I145" t="s">
         <v>29</v>
       </c>
-      <c r="J145" s="1" t="s">
+      <c r="J145" t="s">
         <v>32</v>
       </c>
       <c r="K145" t="s">
@@ -8946,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N145" t="s">
         <v>22</v>
@@ -8963,7 +8965,7 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8989,7 +8991,7 @@
       <c r="I146" t="s">
         <v>29</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="J146" t="s">
         <v>32</v>
       </c>
       <c r="K146" t="s">
@@ -8999,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
@@ -9016,7 +9018,7 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -9042,7 +9044,7 @@
       <c r="I147" t="s">
         <v>29</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="J147" t="s">
         <v>32</v>
       </c>
       <c r="K147" t="s">
@@ -9052,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
@@ -9069,7 +9071,7 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -9095,7 +9097,7 @@
       <c r="I148" t="s">
         <v>29</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="J148" t="s">
         <v>24</v>
       </c>
       <c r="K148" t="s">
@@ -9105,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
@@ -9122,7 +9124,7 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -9148,7 +9150,7 @@
       <c r="I149" t="s">
         <v>29</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="J149" t="s">
         <v>24</v>
       </c>
       <c r="K149" t="s">
@@ -9158,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N149" t="s">
         <v>22</v>
@@ -9175,7 +9177,7 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -9201,7 +9203,7 @@
       <c r="I150" t="s">
         <v>29</v>
       </c>
-      <c r="J150" s="1" t="s">
+      <c r="J150" t="s">
         <v>32</v>
       </c>
       <c r="K150" t="s">
@@ -9211,7 +9213,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N150" t="s">
         <v>22</v>
@@ -9228,7 +9230,7 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -9254,7 +9256,7 @@
       <c r="I151" t="s">
         <v>29</v>
       </c>
-      <c r="J151" s="1" t="s">
+      <c r="J151" t="s">
         <v>32</v>
       </c>
       <c r="K151" t="s">
@@ -9264,7 +9266,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N151" t="s">
         <v>22</v>
@@ -9281,7 +9283,7 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -9307,7 +9309,7 @@
       <c r="I152" t="s">
         <v>29</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="J152" t="s">
         <v>32</v>
       </c>
       <c r="K152" t="s">
@@ -9317,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N152" t="s">
         <v>22</v>
@@ -9334,7 +9336,7 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -9360,7 +9362,7 @@
       <c r="I153" t="s">
         <v>29</v>
       </c>
-      <c r="J153" s="1" t="s">
+      <c r="J153" t="s">
         <v>32</v>
       </c>
       <c r="K153" t="s">
@@ -9370,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N153" t="s">
         <v>22</v>
@@ -9387,7 +9389,7 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -9413,7 +9415,7 @@
       <c r="I154" t="s">
         <v>29</v>
       </c>
-      <c r="J154" s="1" t="s">
+      <c r="J154" t="s">
         <v>19</v>
       </c>
       <c r="K154" t="s">
@@ -9423,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N154" t="s">
         <v>22</v>
@@ -9440,7 +9442,7 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -9466,7 +9468,7 @@
       <c r="I155" t="s">
         <v>29</v>
       </c>
-      <c r="J155" s="1" t="s">
+      <c r="J155" t="s">
         <v>32</v>
       </c>
       <c r="K155" t="s">
@@ -9476,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N155" t="s">
         <v>22</v>
@@ -9493,7 +9495,7 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -9519,7 +9521,7 @@
       <c r="I156" t="s">
         <v>29</v>
       </c>
-      <c r="J156" s="1" t="s">
+      <c r="J156" t="s">
         <v>24</v>
       </c>
       <c r="K156" t="s">
@@ -9529,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N156" t="s">
         <v>22</v>
@@ -9546,7 +9548,7 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -9572,7 +9574,7 @@
       <c r="I157" t="s">
         <v>29</v>
       </c>
-      <c r="J157" s="1" t="s">
+      <c r="J157" t="s">
         <v>19</v>
       </c>
       <c r="K157" t="s">
@@ -9582,7 +9584,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N157" t="s">
         <v>22</v>
@@ -9599,7 +9601,7 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -9625,7 +9627,7 @@
       <c r="I158" t="s">
         <v>29</v>
       </c>
-      <c r="J158" s="1" t="s">
+      <c r="J158" t="s">
         <v>32</v>
       </c>
       <c r="K158" t="s">
@@ -9635,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
@@ -9652,7 +9654,7 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -9678,7 +9680,7 @@
       <c r="I159" t="s">
         <v>29</v>
       </c>
-      <c r="J159" s="1" t="s">
+      <c r="J159" t="s">
         <v>19</v>
       </c>
       <c r="K159" t="s">
@@ -9688,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
@@ -9705,7 +9707,7 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -9731,7 +9733,7 @@
       <c r="I160" t="s">
         <v>29</v>
       </c>
-      <c r="J160" s="1" t="s">
+      <c r="J160" t="s">
         <v>32</v>
       </c>
       <c r="K160" t="s">
@@ -9741,7 +9743,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
@@ -9758,7 +9760,7 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9784,7 +9786,7 @@
       <c r="I161" t="s">
         <v>29</v>
       </c>
-      <c r="J161" s="1" t="s">
+      <c r="J161" t="s">
         <v>32</v>
       </c>
       <c r="K161" t="s">
@@ -9794,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N161" t="s">
         <v>22</v>
@@ -9811,7 +9813,7 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9837,7 +9839,7 @@
       <c r="I162" t="s">
         <v>29</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="J162" t="s">
         <v>32</v>
       </c>
       <c r="K162" t="s">
@@ -9847,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N162" t="s">
         <v>22</v>
@@ -9864,7 +9866,7 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9890,7 +9892,7 @@
       <c r="I163" t="s">
         <v>29</v>
       </c>
-      <c r="J163" s="1" t="s">
+      <c r="J163" t="s">
         <v>32</v>
       </c>
       <c r="K163" t="s">
@@ -9900,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N163" t="s">
         <v>22</v>
@@ -9917,7 +9919,7 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9943,7 +9945,7 @@
       <c r="I164" t="s">
         <v>29</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" t="s">
         <v>32</v>
       </c>
       <c r="K164" t="s">
@@ -9953,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N164" t="s">
         <v>22</v>
@@ -9970,7 +9972,7 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -9996,7 +9998,7 @@
       <c r="I165" t="s">
         <v>29</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" t="s">
         <v>24</v>
       </c>
       <c r="K165" t="s">
@@ -10006,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N165" t="s">
         <v>22</v>
@@ -10024,7 +10026,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q1 A2:I165 K2:Q165" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q1 A2:I36 K2:Q165 A38:I165 B37:I37" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-05-01T05:20:31.762Z</v>
+        <v>2026-05-01T06:06:21.333Z</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-05-01T05:22:04.348Z</v>
+        <v>2026-05-01T06:06:39.052Z</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-05-01T05:27:35.358Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-05-01T05:20:31.762Z</v>
+        <v>2026-05-01T06:06:21.333Z</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-05-01T05:25:30.862Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-05-01T05:21:48.170Z</v>
+        <v>2026-05-01T06:06:32.626Z</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-05-01T05:29:24.760Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-05-01T05:21:48.170Z</v>
+        <v>2026-05-01T06:06:32.626Z</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-01T05:22:04.348Z</v>
+        <v>2026-05-01T06:06:39.052Z</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-05-01T05:27:35.358Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-05-01T05:25:30.862Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-05-01T05:29:24.760Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N16" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -613,19 +613,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vitality</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>1092.8164543706378</v>
+        <v>1099.1220840512854</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-05-01T06:06:39.052Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -666,19 +666,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Vitality</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1084.637381428638</v>
+        <v>1092.8164543706378</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-05-01T06:07:06.437Z</v>
+        <v>2026-05-01T06:06:39.052Z</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -719,19 +719,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Elevate</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1072.2107207632046</v>
+        <v>1078.7064513093121</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J7" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K7" t="str">
         <v>none</v>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-05-01T06:06:21.333Z</v>
+        <v>2026-05-30T04:01:51.528Z</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -772,19 +772,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Eternal Fire</v>
+        <v>Liquid</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>1071.453917138899</v>
+        <v>1076.8669269238046</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-05-01T06:06:54.331Z</v>
+        <v>2026-05-30T04:01:58.103Z</v>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -878,19 +878,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Natus Vincere</v>
+        <v>Elevate</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>1063.0400344220263</v>
+        <v>1056.7441503790217</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J10" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K10" t="str">
         <v>none</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-05-01T06:08:21.905Z</v>
+        <v>2026-05-30T04:01:58.103Z</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -931,19 +931,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Liquid</v>
+        <v>Eternal Fire</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>1061.4003565396217</v>
+        <v>1055.7875002516132</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-05-01T06:06:32.626Z</v>
+        <v>2026-05-30T04:01:51.528Z</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>1060.3818552457028</v>
+        <v>1046.4273525065098</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-01T06:06:39.052Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N12" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -454,19 +454,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The MongolZ</v>
+        <v>Iluminar</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1118.935353572816</v>
+        <v>1140.1972080662238</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -481,7 +481,7 @@
         <v>Tier 2</v>
       </c>
       <c r="J2" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K2" t="str">
         <v>none</v>
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-03-21T04:31:17.566Z</v>
+        <v>2026-06-26T13:18:34.266Z</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -507,19 +507,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nemiga</v>
+        <v>Vitality</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1117.157738135286</v>
+        <v>1123.4589147453712</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -534,7 +534,7 @@
         <v>Tier 2</v>
       </c>
       <c r="J3" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K3" t="str">
         <v>none</v>
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-05-01T06:06:21.333Z</v>
+        <v>2026-06-26T13:18:25.039Z</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -560,19 +560,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Iluminar</v>
+        <v>The MongolZ</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1110.4490389924551</v>
+        <v>1100.4531103179672</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -587,7 +587,7 @@
         <v>Tier 2</v>
       </c>
       <c r="J4" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K4" t="str">
         <v>none</v>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-03-21T04:31:26.612Z</v>
+        <v>2026-06-26T13:17:40.099Z</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -613,19 +613,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Nemiga</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
       <c r="E5">
-        <v>1099.1220840512854</v>
+        <v>1099.5274226676695</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -640,7 +640,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J5" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K5" t="str">
         <v>none</v>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-05-30T04:00:20.081Z</v>
+        <v>2026-06-26T13:18:18.807Z</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -666,19 +666,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Vitality</v>
+        <v>Falcons</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1092.8164543706378</v>
+        <v>1086.7086899158157</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-05-01T06:06:39.052Z</v>
+        <v>2026-06-26T13:20:06.028Z</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -719,19 +719,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Natus Vincere</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>1078.7064513093121</v>
+        <v>1083.0296848572636</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-05-30T04:01:51.528Z</v>
+        <v>2026-06-26T13:17:53.824Z</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -772,19 +772,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Liquid</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>1076.8669269238046</v>
+        <v>1064.5550904053082</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-05-30T04:01:58.103Z</v>
+        <v>2026-06-26T13:18:10.268Z</v>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -825,19 +825,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Falcons</v>
+        <v>Liquid</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1068.2170766580805</v>
+        <v>1064.3973274912723</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-05-01T06:06:32.626Z</v>
+        <v>2026-06-26T13:20:06.028Z</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -1249,19 +1249,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bounty Hunters</v>
+        <v>AMKAL</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1017.2412711985547</v>
+        <v>1029.6796950897065</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J17" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K17" t="str">
         <v>none</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-06-26T13:19:23.768Z</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -1302,19 +1302,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Spirit</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>4</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
       <c r="E18">
-        <v>1016.7402640066111</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1355,19 +1355,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Huns</v>
+        <v>Spirit</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>1015</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J19" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K19" t="str">
         <v>none</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Onyx Ravens</v>
+        <v>The Huns</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1014.9877256835035</v>
+        <v>1015</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TYLOO</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>1014.128742285643</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J21" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K21" t="str">
         <v>none</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OG</v>
+        <v>TYLOO</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1526,7 +1526,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>1013.5266895185538</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J22" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K22" t="str">
         <v>none</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BESTIA</v>
+        <v>OG</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>1005.0046329623956</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>G2</v>
+        <v>BESTIA</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>1002.6421965170028</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>hoorai</v>
+        <v>G2</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1685,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="E25">
-        <v>1000.4888979238718</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>00 Nation</v>
+        <v>FURIA</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>1000</v>
+        <v>1001.9019624181617</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>100 Thieves</v>
+        <v>hoorai</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Aether</v>
+        <v>00 Nation</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J28" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K28" t="str">
         <v>none</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>AMKAL</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J29" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K29" t="str">
         <v>none</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Astana Dragons</v>
+        <v>Aether</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Astralis Talent</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Avangar</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J32" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K32" t="str">
         <v>none</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>B8</v>
+        <v>Avangar</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J33" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K33" t="str">
         <v>none</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>BIG Academy</v>
+        <v>B8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J34" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K34" t="str">
         <v>none</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bravado</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Bravado</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J36" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K36" t="str">
         <v>none</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Counter Logic</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J37" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K37" t="str">
         <v>none</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENCE Academy</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J38" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K38" t="str">
         <v>none</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ESC</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Flash</v>
+        <v>ESC</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>Flash</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FlyQuest RED</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Fnatic</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FORZE</v>
+        <v>Fnatic</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J44" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K44" t="str">
         <v>none</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Gambit</v>
+        <v>FORZE</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>GATERON</v>
+        <v>Gambit</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>GhoulsW</v>
+        <v>GATERON</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J47" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K47" t="str">
         <v>none</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HAVU</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Heroic Academy</v>
+        <v>HAVU</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Hesta</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Immortals</v>
+        <v>Hesta</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J51" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K51" t="str">
         <v>none</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Into the Beach</v>
+        <v>Immortals</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kinguin</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J53" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K53" t="str">
         <v>none</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kONO</v>
+        <v>Kinguin</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>MAD Lions</v>
+        <v>LGB</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>MANA</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J57" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K57" t="str">
         <v>none</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MIBR Academy</v>
+        <v>Misfits</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J58" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K58" t="str">
         <v>none</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Misfits</v>
+        <v>mousesports</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>mousesports</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>MOUZ NXT</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Movistar KOI</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>NIP Impact</v>
+        <v>Nordix</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nordix</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>NOVAQ</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J65" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K65" t="str">
         <v>none</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>paiN Academy</v>
+        <v>QMISTRY</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J66" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K66" t="str">
         <v>none</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>QMISTRY</v>
+        <v>Quantum Bellator Fire</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Quantum Bellator Fire</v>
+        <v>Rogue</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J68" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K68" t="str">
         <v>none</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Rogue</v>
+        <v>Shika</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Shika</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J70" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K70" t="str">
         <v>none</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SKYFURY</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Space Soldiers</v>
+        <v>Sprout</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J72" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K72" t="str">
         <v>none</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Sprout</v>
+        <v>Tsunami</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J73" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K73" t="str">
         <v>none</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tsunami</v>
+        <v>VeryGames</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>VeryGames</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Vox Eminor</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4429,19 +4429,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Wildcard Academy</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J77" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K77" t="str">
         <v>none</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Spirit Academy</v>
+        <v>True Rippers</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4509,7 +4509,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J78" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K78" t="str">
         <v>none</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>True Rippers</v>
+        <v>FaZe</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>FaZe</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>iBUYPOWER</v>
+        <v>GODSENT</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4668,7 +4668,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J81" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K81" t="str">
         <v>none</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>GODSENT</v>
+        <v>M80</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -4706,7 +4706,7 @@
         <v>2</v>
       </c>
       <c r="E82">
-        <v>999.7251809772306</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,19 +4747,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>M80</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>999.672340544519</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Orbit</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -4812,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="E84">
-        <v>999.4408194717619</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J84" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K84" t="str">
         <v>none</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,19 +4853,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Orbit</v>
+        <v>Alliance</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alliance</v>
+        <v>Homyno</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4933,7 +4933,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J86" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K86" t="str">
         <v>none</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Homyno</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J87" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K87" t="str">
         <v>none</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>MenaceGG</v>
+        <v>Solid</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Solid</v>
+        <v>ENCE</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5092,7 +5092,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J89" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K89" t="str">
         <v>none</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ENCE</v>
+        <v>Nexus</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nexus</v>
+        <v>MIBR</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5198,7 +5198,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J91" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K91" t="str">
         <v>none</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>MIBR</v>
+        <v>Wizards</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -5236,7 +5236,7 @@
         <v>2</v>
       </c>
       <c r="E92">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Wizards</v>
+        <v>RED Canids</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93">
-        <v>999.4062521695108</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>RED Canids</v>
+        <v>Rebels</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94">
-        <v>999.3397745397444</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,19 +5383,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Rebels</v>
+        <v>ad hoc</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>999.3232682842747</v>
+        <v>985</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,19 +5436,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FURIA</v>
+        <v>SAW</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96">
-        <v>985.3605394813516</v>
+        <v>985</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J96" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K96" t="str">
         <v>none</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-19T22:08:26.017Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ad hoc</v>
+        <v>NomadS</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SAW</v>
+        <v>Outsiders</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>NomadS</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J99" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K99" t="str">
         <v>none</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Outsiders</v>
+        <v>The Dice</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Red Viperz</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J101" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K101" t="str">
         <v>none</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Dice</v>
+        <v>ODDIK</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Victores Sumus</v>
+        <v>Qiang</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J103" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K103" t="str">
         <v>none</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:48:45.055Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ODDIK</v>
+        <v>inSanitY</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5887,7 +5887,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J104" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K104" t="str">
         <v>none</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Qiang</v>
+        <v>Sangal</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>inSanitY</v>
+        <v>9Pandas</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Sangal</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>9Pandas</v>
+        <v>CatEvil</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Gods Reign</v>
+        <v>Carnival</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>CatEvil</v>
+        <v>Evil Geniuses</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:47:36.482Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Carnival</v>
+        <v>Vantage</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Evil Geniuses</v>
+        <v>ATOX</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
+        <v>2026-02-19T00:47:18.470Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Vantage</v>
+        <v>Skinvault</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ATOX</v>
+        <v>BC.Game</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J114" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K114" t="str">
         <v>none</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
+        <v>2026-02-19T00:46:52.846Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Skinvault</v>
+        <v>Wings Up</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6470,7 +6470,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J115" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K115" t="str">
         <v>none</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>BC.Game</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J116" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K116" t="str">
         <v>none</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
+        <v>2026-02-19T00:46:08.336Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Wings Up</v>
+        <v>Tricked</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6576,7 +6576,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J117" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K117" t="str">
         <v>none</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-19T00:45:42.234Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Lynn Vision</v>
+        <v>3DMAX</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J118" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K118" t="str">
         <v>none</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
+        <v>2026-02-19T00:39:02.710Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Tricked</v>
+        <v>Venom</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3DMAX</v>
+        <v>ARCRED</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
+        <v>2026-02-19T00:38:03.598Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Venom</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ARCRED</v>
+        <v>Passion UA</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
+        <v>2026-02-19T00:37:27.234Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>GamerLegion</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-19T00:37:20.280Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Passion UA</v>
+        <v>Envy</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
+        <v>2026-02-19T00:37:05.560Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>FlyQuest</v>
+        <v>BIG</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7000,7 +7000,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J125" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K125" t="str">
         <v>none</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
+        <v>2026-02-19T00:36:43.463Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Envy</v>
+        <v>Limitless</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
+        <v>2026-02-19T00:36:26.343Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>BIG</v>
+        <v>Galorys</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J127" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K127" t="str">
         <v>none</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Limitless</v>
+        <v>devils.one</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J128" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K128" t="str">
         <v>none</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Galorys</v>
+        <v>Luminosity</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:23:18.851Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>devils.one</v>
+        <v>Sharks</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J130" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K130" t="str">
         <v>none</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Luminosity</v>
+        <v>IHC</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
+        <v>2026-02-18T21:23:06.529Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Sharks</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>IHC</v>
+        <v>Complexity</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Kappa Bar</v>
+        <v>Case</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Complexity</v>
+        <v>Mythic</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-18T21:22:32.047Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Case</v>
+        <v>Enemy</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-18T21:22:20.745Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Mythic</v>
+        <v>KRU</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-18T21:22:32.047Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Enemy</v>
+        <v>Imperial</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J138" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K138" t="str">
         <v>none</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
+        <v>2026-02-18T21:21:57.658Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,7 +7715,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>KRU</v>
+        <v>9z</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-18T21:21:44.273Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Imperial</v>
+        <v>paiN</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>9z</v>
+        <v>Vexed</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -7848,7 +7848,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J141" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K141" t="str">
         <v>none</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-18T21:21:44.273Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,19 +7874,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>paiN</v>
+        <v>Dignitas</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7901,7 +7901,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J142" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K142" t="str">
         <v>none</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,19 +7927,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Vexed</v>
+        <v>LDLC</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T21:53:53.691Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Dignitas</v>
+        <v>Aravt</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-02-19T02:51:09.872Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>LDLC</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Aravt</v>
+        <v>Entropiq</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8113,7 +8113,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J146" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K146" t="str">
         <v>none</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
+        <v>2026-02-19T02:49:25.044Z</v>
       </c>
       <c r="N146" t="str">
         <v/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>VP.Prodigy</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -8166,7 +8166,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J147" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K147" t="str">
         <v>none</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-02-19T02:49:14.876Z</v>
       </c>
       <c r="N147" t="str">
         <v/>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Entropiq</v>
+        <v>Underground</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J148" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K148" t="str">
         <v>none</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-02-19T02:49:25.044Z</v>
+        <v>2026-02-19T02:47:27.422Z</v>
       </c>
       <c r="N148" t="str">
         <v/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Take Flyte</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -8272,7 +8272,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J149" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K149" t="str">
         <v>none</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-02-19T02:49:14.876Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N149" t="str">
         <v/>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Underground</v>
+        <v>ShindeN</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N150" t="str">
         <v/>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Virtus.pro</v>
+        <v>Permitta</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-02-19T02:36:17.329Z</v>
       </c>
       <c r="N151" t="str">
         <v/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ShindeN</v>
+        <v>Wildcard</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -8431,7 +8431,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J152" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K152" t="str">
         <v>none</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N152" t="str">
         <v/>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Permitta</v>
+        <v>Astralis</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
+        <v>2026-02-19T02:34:01.822Z</v>
       </c>
       <c r="N153" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Wildcard</v>
+        <v>Bad News Eagles</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -8537,7 +8537,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J154" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K154" t="str">
         <v>none</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-02-19T01:45:27.335Z</v>
       </c>
       <c r="N154" t="str">
         <v/>
@@ -8563,7 +8563,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Astralis</v>
+        <v>SK</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -8590,7 +8590,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J155" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K155" t="str">
         <v>none</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N155" t="str">
         <v/>
@@ -8616,7 +8616,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Bad News Eagles</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -8643,7 +8643,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J156" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K156" t="str">
         <v>none</v>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
+        <v>2026-02-19T01:39:12.540Z</v>
       </c>
       <c r="N156" t="str">
         <v/>
@@ -8669,7 +8669,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SK</v>
+        <v>MIBR Academy</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -8681,7 +8681,7 @@
         <v>2</v>
       </c>
       <c r="E157">
-        <v>984.7039370196626</v>
+        <v>984.075576101157</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J157" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K157" t="str">
         <v>none</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N157" t="str">
         <v/>
@@ -8722,19 +8722,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ECSTATIC</v>
+        <v>TALON</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E158">
-        <v>984.7039370196626</v>
+        <v>983.9905713816794</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J158" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K158" t="str">
         <v>none</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
+        <v>2026-02-28T06:27:14.538Z</v>
       </c>
       <c r="N158" t="str">
         <v/>
@@ -8775,19 +8775,19 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>TALON</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E159">
-        <v>983.9905713816794</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -8802,7 +8802,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J159" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K159" t="str">
         <v>none</v>
@@ -8811,7 +8811,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N159" t="str">
         <v/>
@@ -8828,19 +8828,19 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>NAVI Junior</v>
+        <v>Ninjas in Pyjamas</v>
       </c>
       <c r="B160">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C160">
         <v>0</v>
       </c>
       <c r="D160">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E160">
-        <v>983.2698348870488</v>
+        <v>970</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-02-19T21:53:46.615Z</v>
       </c>
       <c r="N160" t="str">
         <v/>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Ninjas in Pyjamas</v>
+        <v>MOUZ</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -8917,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="str">
-        <v>2026-02-19T21:53:46.615Z</v>
+        <v>2026-02-19T21:53:40.004Z</v>
       </c>
       <c r="N161" t="str">
         <v/>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>MOUZ</v>
+        <v>Aurora</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="str">
-        <v>2026-02-19T21:53:40.004Z</v>
+        <v>2026-02-19T21:53:30.387Z</v>
       </c>
       <c r="N162" t="str">
         <v/>
@@ -8987,7 +8987,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Aurora</v>
+        <v>Reason</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="str">
-        <v>2026-02-19T21:53:30.387Z</v>
+        <v>2026-02-19T21:53:23.315Z</v>
       </c>
       <c r="N163" t="str">
         <v/>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Reason</v>
+        <v>MANA</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9052,7 +9052,7 @@
         <v>2</v>
       </c>
       <c r="E164">
-        <v>970</v>
+        <v>969.3956084954185</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -9067,7 +9067,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J164" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K164" t="str">
         <v>none</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="M164" t="str">
-        <v>2026-02-19T21:53:23.315Z</v>
+        <v>2026-06-26T13:19:16.424Z</v>
       </c>
       <c r="N164" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -1408,7 +1408,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Take Flyte</v>
+        <v>Entropiq</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -1420,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>1015.6724304703677</v>
+        <v>1016.3039403297893</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-07-05T04:05:23.392Z</v>
+        <v>2026-07-07T04:08:42.949Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Huns</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1015</v>
+        <v>1015.6724304703677</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-07-05T04:05:23.392Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Onyx Ravens</v>
+        <v>The Huns</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1014.9877256835035</v>
+        <v>1015</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TYLOO</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>1014.128742285643</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>OG</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>1013.5266895185538</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Into the Beach</v>
+        <v>TYLOO</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1011.823225766436</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J25" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K25" t="str">
         <v>none</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>BESTIA</v>
+        <v>OG</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>1005.0046329623956</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>G2</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>1002.6421965170028</v>
+        <v>1011.823225766436</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J27" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K27" t="str">
         <v>none</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FURIA</v>
+        <v>BESTIA</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>1001.9019624181617</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Mythic</v>
+        <v>G2</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1000.942849124707</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J29" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K29" t="str">
         <v>none</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>hoorai</v>
+        <v>FURIA</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>1000.4888979238718</v>
+        <v>1001.9019624181617</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>00 Nation</v>
+        <v>Mythic</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>1000.942849124707</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J31" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K31" t="str">
         <v>none</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>100 Thieves</v>
+        <v>hoorai</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Astana Dragons</v>
+        <v>00 Nation</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Astralis Talent</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Avangar</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BIG Academy</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Counter Logic</v>
+        <v>Bravado</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENCE Academy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ESC</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Flash</v>
+        <v>ESC</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>Flash</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FlyQuest RED</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Fnatic</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>FORZE</v>
+        <v>Fnatic</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gambit</v>
+        <v>FORZE</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J47" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K47" t="str">
         <v>none</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>GATERON</v>
+        <v>Gambit</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J48" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K48" t="str">
         <v>none</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>GhoulsW</v>
+        <v>GATERON</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J49" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K49" t="str">
         <v>none</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HAVU</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Heroic Academy</v>
+        <v>HAVU</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hesta</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kinguin</v>
+        <v>Hesta</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kONO</v>
+        <v>Kinguin</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>MAD Lions</v>
+        <v>LGB</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Misfits</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mousesports</v>
+        <v>Misfits</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MOUZ NXT</v>
+        <v>mousesports</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Movistar KOI</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>NIP Impact</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nordix</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>NOVAQ</v>
+        <v>Nordix</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>paiN Academy</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J64" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K64" t="str">
         <v>none</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sprout</v>
+        <v>Tsunami</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J71" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K71" t="str">
         <v>none</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Tsunami</v>
+        <v>VeryGames</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>VeryGames</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Vox Eminor</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Wildcard Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4376,19 +4376,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lux Tenebris</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Spirit Academy</v>
+        <v>True Rippers</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4456,7 +4456,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J77" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K77" t="str">
         <v>none</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>True Rippers</v>
+        <v>FaZe</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>FaZe</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>iBUYPOWER</v>
+        <v>GODSENT</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>GODSENT</v>
+        <v>M80</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4653,7 +4653,7 @@
         <v>2</v>
       </c>
       <c r="E81">
-        <v>999.7251809772306</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>M80</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>999.672340544519</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J82" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K82" t="str">
         <v>none</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Orbit</v>
       </c>
       <c r="B83">
         <v>3</v>
@@ -4759,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="E83">
-        <v>999.4408194717619</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,19 +4800,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Orbit</v>
+        <v>Alliance</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alliance</v>
+        <v>Homyno</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -4880,7 +4880,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J85" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K85" t="str">
         <v>none</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Homyno</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4933,7 +4933,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J86" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K86" t="str">
         <v>none</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MenaceGG</v>
+        <v>Solid</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J87" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K87" t="str">
         <v>none</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Solid</v>
+        <v>ENCE</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ENCE</v>
+        <v>Nexus</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nexus</v>
+        <v>MIBR</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -5145,7 +5145,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J90" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K90" t="str">
         <v>none</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MIBR</v>
+        <v>Wizards</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="E91">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,19 +5224,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Wizards</v>
+        <v>RED Canids</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>999.4062521695108</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>RED Canids</v>
+        <v>Rebels</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93">
-        <v>999.3397745397444</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J93" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K93" t="str">
         <v>none</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Rebels</v>
+        <v>Legacy</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94">
-        <v>999.3232682842747</v>
+        <v>991.3908681786203</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-05T04:07:08.327Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,19 +5383,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Legacy</v>
+        <v>ad hoc</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>991.3908681786203</v>
+        <v>985</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-07-05T04:07:08.327Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ad hoc</v>
+        <v>SAW</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J96" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K96" t="str">
         <v>none</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SAW</v>
+        <v>NomadS</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J97" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K97" t="str">
         <v>none</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>NomadS</v>
+        <v>Outsiders</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J98" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K98" t="str">
         <v>none</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Outsiders</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J99" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K99" t="str">
         <v>none</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Red Viperz</v>
+        <v>The Dice</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J100" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K100" t="str">
         <v>none</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Dice</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J101" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K101" t="str">
         <v>none</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Victores Sumus</v>
+        <v>ODDIK</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ODDIK</v>
+        <v>Qiang</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J103" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K103" t="str">
         <v>none</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:48:45.055Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Qiang</v>
+        <v>inSanitY</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>inSanitY</v>
+        <v>Sangal</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Sangal</v>
+        <v>9Pandas</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>9Pandas</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Gods Reign</v>
+        <v>CatEvil</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>CatEvil</v>
+        <v>Carnival</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Carnival</v>
+        <v>Evil Geniuses</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-19T00:47:36.482Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Evil Geniuses</v>
+        <v>Vantage</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Vantage</v>
+        <v>ATOX</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-19T00:47:18.470Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ATOX</v>
+        <v>Skinvault</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J113" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K113" t="str">
         <v>none</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Skinvault</v>
+        <v>BC.Game</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-19T00:46:52.846Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>BC.Game</v>
+        <v>Wings Up</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6470,7 +6470,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J115" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K115" t="str">
         <v>none</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Wings Up</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-19T00:46:08.336Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Lynn Vision</v>
+        <v>Tricked</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6576,7 +6576,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J117" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K117" t="str">
         <v>none</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
+        <v>2026-02-19T00:45:42.234Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Tricked</v>
+        <v>3DMAX</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
+        <v>2026-02-19T00:39:02.710Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3DMAX</v>
+        <v>Venom</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Venom</v>
+        <v>ARCRED</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J120" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K120" t="str">
         <v>none</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-19T00:38:03.598Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ARCRED</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J121" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K121" t="str">
         <v>none</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>GamerLegion</v>
+        <v>Passion UA</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J122" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K122" t="str">
         <v>none</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-19T00:37:27.234Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Passion UA</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
+        <v>2026-02-19T00:37:20.280Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>FlyQuest</v>
+        <v>Envy</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J124" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K124" t="str">
         <v>none</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
+        <v>2026-02-19T00:37:05.560Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Envy</v>
+        <v>BIG</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
+        <v>2026-02-19T00:36:43.463Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>BIG</v>
+        <v>Limitless</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
+        <v>2026-02-19T00:36:26.343Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Limitless</v>
+        <v>Galorys</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J127" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K127" t="str">
         <v>none</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Galorys</v>
+        <v>devils.one</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J128" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K128" t="str">
         <v>none</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>devils.one</v>
+        <v>Luminosity</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:23:18.851Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Luminosity</v>
+        <v>Sharks</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J130" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K130" t="str">
         <v>none</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sharks</v>
+        <v>IHC</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-02-18T21:23:06.529Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>IHC</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kappa Bar</v>
+        <v>Complexity</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Complexity</v>
+        <v>Case</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J134" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K134" t="str">
         <v>none</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Case</v>
+        <v>Enemy</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-18T21:22:20.745Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Enemy</v>
+        <v>KRU</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J136" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K136" t="str">
         <v>none</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>KRU</v>
+        <v>Imperial</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-18T21:21:57.658Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Imperial</v>
+        <v>paiN</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,7 +7715,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>paiN</v>
+        <v>Vexed</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J139" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K139" t="str">
         <v>none</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,19 +7768,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Vexed</v>
+        <v>Dignitas</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dignitas</v>
+        <v>LDLC</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-02-19T21:53:53.691Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>LDLC</v>
+        <v>Aravt</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
+        <v>2026-02-19T02:51:09.872Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Aravt</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>VP.Prodigy</v>
+        <v>Underground</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-02-19T02:47:27.422Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Entropiq</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8060,7 +8060,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J145" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K145" t="str">
         <v>none</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-02-19T02:49:25.044Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Underground</v>
+        <v>ShindeN</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N146" t="str">
         <v/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Virtus.pro</v>
+        <v>Permitta</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-02-19T02:36:17.329Z</v>
       </c>
       <c r="N147" t="str">
         <v/>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ShindeN</v>
+        <v>Wildcard</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J148" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K148" t="str">
         <v>none</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N148" t="str">
         <v/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Permitta</v>
+        <v>Astralis</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
+        <v>2026-02-19T02:34:01.822Z</v>
       </c>
       <c r="N149" t="str">
         <v/>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Wildcard</v>
+        <v>Bad News Eagles</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J150" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K150" t="str">
         <v>none</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-02-19T01:45:27.335Z</v>
       </c>
       <c r="N150" t="str">
         <v/>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Astralis</v>
+        <v>SK</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J151" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K151" t="str">
         <v>none</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N151" t="str">
         <v/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Bad News Eagles</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -8431,7 +8431,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J152" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K152" t="str">
         <v>none</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
+        <v>2026-02-19T01:39:12.540Z</v>
       </c>
       <c r="N152" t="str">
         <v/>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SK</v>
+        <v>MIBR Academy</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -8469,7 +8469,7 @@
         <v>2</v>
       </c>
       <c r="E153">
-        <v>984.7039370196626</v>
+        <v>984.075576101157</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J153" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K153" t="str">
         <v>none</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N153" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ECSTATIC</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="E154">
-        <v>984.7039370196626</v>
+        <v>984.0732769617838</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8537,7 +8537,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J154" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K154" t="str">
         <v>none</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N154" t="str">
         <v/>
@@ -8563,19 +8563,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>MIBR Academy</v>
+        <v>TALON</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155">
-        <v>984.075576101157</v>
+        <v>983.9905713816794</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J155" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K155" t="str">
         <v>none</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:27:14.538Z</v>
       </c>
       <c r="N155" t="str">
         <v/>
@@ -8616,19 +8616,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>TALON</v>
+        <v>B8</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156">
-        <v>983.9905713816794</v>
+        <v>983.4284201175154</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J156" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K156" t="str">
         <v>none</v>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N156" t="str">
         <v/>
@@ -8669,19 +8669,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>B8</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E157">
-        <v>983.4284201175154</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J157" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K157" t="str">
         <v>none</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N157" t="str">
         <v/>
@@ -8722,19 +8722,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>NAVI Junior</v>
+        <v>9z</v>
       </c>
       <c r="B158">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E158">
-        <v>983.2698348870488</v>
+        <v>971.3809496889581</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J158" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K158" t="str">
         <v>none</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N158" t="str">
         <v/>
@@ -8775,19 +8775,19 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>9z</v>
+        <v>Ninjas in Pyjamas</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159">
-        <v>971.3809496889581</v>
+        <v>970</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -8802,7 +8802,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J159" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K159" t="str">
         <v>none</v>
@@ -8811,7 +8811,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-19T21:53:46.615Z</v>
       </c>
       <c r="N159" t="str">
         <v/>
@@ -8828,7 +8828,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Ninjas in Pyjamas</v>
+        <v>MOUZ</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="str">
-        <v>2026-02-19T21:53:46.615Z</v>
+        <v>2026-02-19T21:53:40.004Z</v>
       </c>
       <c r="N160" t="str">
         <v/>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>MOUZ</v>
+        <v>Aurora</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -8917,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="str">
-        <v>2026-02-19T21:53:40.004Z</v>
+        <v>2026-02-19T21:53:30.387Z</v>
       </c>
       <c r="N161" t="str">
         <v/>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Aurora</v>
+        <v>Reason</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="str">
-        <v>2026-02-19T21:53:30.387Z</v>
+        <v>2026-02-19T21:53:23.315Z</v>
       </c>
       <c r="N162" t="str">
         <v/>
@@ -8987,7 +8987,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Reason</v>
+        <v>Sprout</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -8999,7 +8999,7 @@
         <v>2</v>
       </c>
       <c r="E163">
-        <v>970</v>
+        <v>969.9715073660867</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J163" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K163" t="str">
         <v>none</v>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="str">
-        <v>2026-02-19T21:53:23.315Z</v>
+        <v>2026-07-07T04:07:21.355Z</v>
       </c>
       <c r="N163" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -469,7 +469,7 @@
         <v>1155.8269573717953</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -484,13 +484,13 @@
         <v>AM</v>
       </c>
       <c r="K2" t="str">
-        <v>none</v>
+        <v>major</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-05T04:08:18.328Z</v>
+        <v>2026-07-07T13:04:25.872Z</v>
       </c>
       <c r="N2" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -984,19 +984,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Titan</v>
+        <v>FURIA</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>1046.4273525065098</v>
+        <v>1050.7178542874221</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-30T04:00:20.081Z</v>
+        <v>2026-07-23T22:16:25.593Z</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1037,19 +1037,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Verdant</v>
+        <v>Titan</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>1038.7190184710753</v>
+        <v>1046.4273525065098</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J13" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K13" t="str">
         <v>none</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-02-28T06:29:24.671Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1090,19 +1090,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>PARIVISION</v>
+        <v>AMKAL</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>1034.630067328374</v>
+        <v>1041.3191963490904</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1117,7 +1117,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J14" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K14" t="str">
         <v>none</v>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-05-01T06:07:06.437Z</v>
+        <v>2026-07-23T22:16:25.593Z</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cloud9</v>
+        <v>Verdant</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1031.0582679094105</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J15" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K15" t="str">
         <v>none</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-05-01T06:06:54.331Z</v>
+        <v>2026-02-28T06:29:24.671Z</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Heroic</v>
+        <v>PARIVISION</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1208,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>1030.413991476608</v>
+        <v>1034.630067328374</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-05-01T06:08:21.905Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -1249,19 +1249,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AMKAL</v>
+        <v>Cloud9</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>1029.6796950897065</v>
+        <v>1031.0582679094105</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J17" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K17" t="str">
         <v>none</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-06-26T13:19:23.768Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Bounty Hunters</v>
+        <v>Heroic</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -1311,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1017.2412711985547</v>
+        <v>1030.413991476608</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1355,19 +1355,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Spirit</v>
+        <v>Entropiq</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>1016.7402640066111</v>
+        <v>1029.3999079514006</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J19" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K19" t="str">
         <v>none</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Entropiq</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>1016.3039403297893</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J20" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K20" t="str">
         <v>none</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-07-07T04:08:42.949Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Take Flyte</v>
+        <v>Spirit</v>
       </c>
       <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>3</v>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
       <c r="E21">
-        <v>1015.6724304703677</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J21" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K21" t="str">
         <v>none</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-07-05T04:05:23.392Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Into the Beach</v>
+        <v>BESTIA</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>1011.823225766436</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BESTIA</v>
+        <v>G2</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>1005.0046329623956</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J28" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K28" t="str">
         <v>none</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>G2</v>
+        <v>hoorai</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -1897,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>1002.6421965170028</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FURIA</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>1001.9019624181617</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mythic</v>
+        <v>00 Nation</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1000.942849124707</v>
+        <v>1000</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J31" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K31" t="str">
         <v>none</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v/>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>hoorai</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1000.4888979238718</v>
+        <v>1000</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v/>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>00 Nation</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>100 Thieves</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Astana Dragons</v>
+        <v>Avangar</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Astralis Talent</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Avangar</v>
+        <v>Bravado</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>BIG Academy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bravado</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>ESC</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENCE Academy</v>
+        <v>Flash</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ESC</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Flash</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>Fnatic</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FlyQuest RED</v>
+        <v>FORZE</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Fnatic</v>
+        <v>Gambit</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Gambit</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>GATERON</v>
+        <v>HAVU</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J49" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K49" t="str">
         <v>none</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>GhoulsW</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HAVU</v>
+        <v>Hesta</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Heroic Academy</v>
+        <v>Kinguin</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hesta</v>
+        <v>kONO</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J53" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K53" t="str">
         <v>none</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Kinguin</v>
+        <v>LGB</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>kONO</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J55" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K55" t="str">
         <v>none</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>LGB</v>
+        <v>Misfits</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>MAD Lions</v>
+        <v>mousesports</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Misfits</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>mousesports</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MOUZ NXT</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Movistar KOI</v>
+        <v>Nordix</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>NIP Impact</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nordix</v>
+        <v>QMISTRY</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>NOVAQ</v>
+        <v>Quantum Bellator Fire</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>QMISTRY</v>
+        <v>Rogue</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J65" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K65" t="str">
         <v>none</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quantum Bellator Fire</v>
+        <v>Shika</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J66" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K66" t="str">
         <v>none</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Rogue</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J67" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K67" t="str">
         <v>none</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Shika</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J68" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K68" t="str">
         <v>none</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SKYFURY</v>
+        <v>Tsunami</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Space Soldiers</v>
+        <v>VeryGames</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tsunami</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>VeryGames</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Vox Eminor</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J73" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K73" t="str">
         <v>none</v>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Wildcard Academy</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J74" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K74" t="str">
         <v>none</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4323,19 +4323,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lux Tenebris</v>
+        <v>True Rippers</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N75" t="str">
         <v/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Spirit Academy</v>
+        <v>FaZe</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>True Rippers</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>FaZe</v>
+        <v>GODSENT</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4509,7 +4509,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J78" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K78" t="str">
         <v>none</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>iBUYPOWER</v>
+        <v>M80</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4547,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <v>999.7251809772306</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J79" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K79" t="str">
         <v>none</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,19 +4588,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>GODSENT</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>999.7251809772306</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>M80</v>
+        <v>Orbit</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>999.672340544519</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J81" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K81" t="str">
         <v>none</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Alliance</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>999.4408194717619</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J82" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K82" t="str">
         <v>none</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,19 +4747,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Orbit</v>
+        <v>Homyno</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alliance</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Homyno</v>
+        <v>Solid</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MenaceGG</v>
+        <v>ENCE</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Solid</v>
+        <v>Nexus</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J87" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K87" t="str">
         <v>none</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ENCE</v>
+        <v>MIBR</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nexus</v>
+        <v>Wizards</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5077,7 +5077,7 @@
         <v>2</v>
       </c>
       <c r="E89">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J89" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K89" t="str">
         <v>none</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,19 +5118,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MIBR</v>
+        <v>RED Canids</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90">
-        <v>999.4088515186523</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,19 +5171,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Wizards</v>
+        <v>Rebels</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91">
-        <v>999.4062521695108</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J91" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K91" t="str">
         <v>none</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,19 +5224,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>RED Canids</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>999.3397745397444</v>
+        <v>996.0904918173039</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-07-23T22:12:51.919Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Rebels</v>
+        <v>Mythic</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93">
-        <v>999.3232682842747</v>
+        <v>986.2948766874508</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J93" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K93" t="str">
         <v>none</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-23T22:00:15.992Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Legacy</v>
+        <v>ad hoc</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>991.3908681786203</v>
+        <v>985</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-07-05T04:07:08.327Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ad hoc</v>
+        <v>SAW</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SAW</v>
+        <v>NomadS</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J96" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K96" t="str">
         <v>none</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>NomadS</v>
+        <v>Outsiders</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J97" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K97" t="str">
         <v>none</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Outsiders</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J98" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K98" t="str">
         <v>none</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Red Viperz</v>
+        <v>The Dice</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J99" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K99" t="str">
         <v>none</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Dice</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J100" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K100" t="str">
         <v>none</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Victores Sumus</v>
+        <v>ODDIK</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J101" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K101" t="str">
         <v>none</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ODDIK</v>
+        <v>Qiang</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:48:45.055Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Qiang</v>
+        <v>inSanitY</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>inSanitY</v>
+        <v>Sangal</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Sangal</v>
+        <v>9Pandas</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>9Pandas</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Gods Reign</v>
+        <v>CatEvil</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>CatEvil</v>
+        <v>Carnival</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Carnival</v>
+        <v>Evil Geniuses</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-19T00:47:36.482Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Evil Geniuses</v>
+        <v>Vantage</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Vantage</v>
+        <v>ATOX</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J111" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K111" t="str">
         <v>none</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-19T00:47:18.470Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ATOX</v>
+        <v>Skinvault</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Skinvault</v>
+        <v>BC.Game</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-19T00:46:52.846Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BC.Game</v>
+        <v>Wings Up</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J114" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K114" t="str">
         <v>none</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Wings Up</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-19T00:46:08.336Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Lynn Vision</v>
+        <v>Tricked</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J116" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K116" t="str">
         <v>none</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
+        <v>2026-02-19T00:45:42.234Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tricked</v>
+        <v>3DMAX</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
+        <v>2026-02-19T00:39:02.710Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3DMAX</v>
+        <v>Venom</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J118" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K118" t="str">
         <v>none</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Venom</v>
+        <v>ARCRED</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-19T00:38:03.598Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ARCRED</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J120" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K120" t="str">
         <v>none</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>GamerLegion</v>
+        <v>Passion UA</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J121" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K121" t="str">
         <v>none</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-19T00:37:27.234Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Passion UA</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J122" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K122" t="str">
         <v>none</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
+        <v>2026-02-19T00:37:20.280Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>FlyQuest</v>
+        <v>Envy</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
+        <v>2026-02-19T00:37:05.560Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Envy</v>
+        <v>BIG</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
+        <v>2026-02-19T00:36:43.463Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>BIG</v>
+        <v>Limitless</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
+        <v>2026-02-19T00:36:26.343Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Limitless</v>
+        <v>Galorys</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J126" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K126" t="str">
         <v>none</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Galorys</v>
+        <v>devils.one</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J127" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K127" t="str">
         <v>none</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>devils.one</v>
+        <v>Luminosity</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J128" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K128" t="str">
         <v>none</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:23:18.851Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Luminosity</v>
+        <v>Sharks</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Sharks</v>
+        <v>IHC</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J130" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K130" t="str">
         <v>none</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-02-18T21:23:06.529Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>IHC</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Kappa Bar</v>
+        <v>Complexity</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Complexity</v>
+        <v>Case</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Case</v>
+        <v>Enemy</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-18T21:22:20.745Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Enemy</v>
+        <v>KRU</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -7530,7 +7530,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J135" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K135" t="str">
         <v>none</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>KRU</v>
+        <v>Imperial</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-18T21:21:57.658Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Imperial</v>
+        <v>paiN</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>paiN</v>
+        <v>Vexed</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J138" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K138" t="str">
         <v>none</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,19 +7715,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Vexed</v>
+        <v>Dignitas</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dignitas</v>
+        <v>LDLC</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-02-19T21:53:53.691Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>LDLC</v>
+        <v>Aravt</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
+        <v>2026-02-19T02:51:09.872Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Aravt</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>VP.Prodigy</v>
+        <v>Underground</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-02-19T02:47:27.422Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Underground</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Virtus.pro</v>
+        <v>ShindeN</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ShindeN</v>
+        <v>Permitta</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-02-19T02:36:17.329Z</v>
       </c>
       <c r="N146" t="str">
         <v/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Permitta</v>
+        <v>Wildcard</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -8166,7 +8166,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J147" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K147" t="str">
         <v>none</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N147" t="str">
         <v/>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wildcard</v>
+        <v>Astralis</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J148" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K148" t="str">
         <v>none</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-02-19T02:34:01.822Z</v>
       </c>
       <c r="N148" t="str">
         <v/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Astralis</v>
+        <v>Bad News Eagles</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -8272,7 +8272,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J149" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K149" t="str">
         <v>none</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
+        <v>2026-02-19T01:45:27.335Z</v>
       </c>
       <c r="N149" t="str">
         <v/>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Bad News Eagles</v>
+        <v>SK</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J150" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K150" t="str">
         <v>none</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N150" t="str">
         <v/>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SK</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J151" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K151" t="str">
         <v>none</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-02-19T01:39:12.540Z</v>
       </c>
       <c r="N151" t="str">
         <v/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ECSTATIC</v>
+        <v>MIBR Academy</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -8416,7 +8416,7 @@
         <v>2</v>
       </c>
       <c r="E152">
-        <v>984.7039370196626</v>
+        <v>984.075576101157</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J152" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K152" t="str">
         <v>none</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N152" t="str">
         <v/>
@@ -8457,19 +8457,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>MIBR Academy</v>
+        <v>TALON</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E153">
-        <v>984.075576101157</v>
+        <v>983.9905713816794</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J153" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K153" t="str">
         <v>none</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:27:14.538Z</v>
       </c>
       <c r="N153" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>paiN Academy</v>
+        <v>B8</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="E154">
-        <v>984.0732769617838</v>
+        <v>983.4284201175154</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="str">
-        <v>2026-07-07T04:08:50.601Z</v>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N154" t="str">
         <v/>
@@ -8563,19 +8563,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>TALON</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E155">
-        <v>983.9905713816794</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J155" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K155" t="str">
         <v>none</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N155" t="str">
         <v/>
@@ -8616,19 +8616,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>B8</v>
+        <v>Legacy</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E156">
-        <v>983.4284201175154</v>
+        <v>976.9354856610739</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-07-23T22:02:02.134Z</v>
       </c>
       <c r="N156" t="str">
         <v/>
@@ -8669,19 +8669,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>NAVI Junior</v>
+        <v>9z</v>
       </c>
       <c r="B157">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E157">
-        <v>983.2698348870488</v>
+        <v>971.3809496889581</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J157" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K157" t="str">
         <v>none</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N157" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>9z</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -8734,7 +8734,7 @@
         <v>3</v>
       </c>
       <c r="E158">
-        <v>971.3809496889581</v>
+        <v>971.0310326935038</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-07-23T22:01:33.382Z</v>
       </c>
       <c r="N158" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -469,7 +469,7 @@
         <v>1155.8269573717953</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>12</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-07T13:04:25.872Z</v>
+        <v>2026-07-23T22:29:15.026Z</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>Tier 3</v>
@@ -1014,13 +1014,13 @@
         <v>AM</v>
       </c>
       <c r="K12" t="str">
-        <v>none</v>
+        <v>regional</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-07-23T22:16:25.593Z</v>
+        <v>2026-07-23T22:29:09.347Z</v>
       </c>
       <c r="N12" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Onyx Ravens</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1014.9877256835035</v>
+        <v>1015</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-07-30T05:39:12.741Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Counter Logic</v>
+        <v>Fnatic</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1014.6510123894305</v>
+        <v>1015</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-07-07T04:08:50.601Z</v>
+        <v>2026-07-30T05:39:19.440Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TYLOO</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1014.128742285643</v>
+        <v>1015</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J25" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K25" t="str">
         <v>none</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-07-30T05:41:42.732Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OG</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1013.5266895185538</v>
+        <v>1015</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-07-30T05:41:55.808Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>BESTIA</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1005.0046329623956</v>
+        <v>1015</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J27" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K27" t="str">
         <v>none</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-07-30T05:42:06.941Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>G2</v>
+        <v>mousesports</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1002.6421965170028</v>
+        <v>1015</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-07-30T05:42:44.510Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>hoorai</v>
+        <v>Gambit</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>1000.4888979238718</v>
+        <v>1015</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v>2026-07-30T05:42:49.775Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Take Flyte</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1000.3086743488057</v>
+        <v>1015</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-07-23T22:14:26.816Z</v>
+        <v>2026-07-30T05:42:58.796Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>00 Nation</v>
+        <v>VeryGames</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>2026-07-30T05:43:07.819Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>100 Thieves</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>2026-07-30T05:43:19.675Z</v>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>2026-07-30T05:43:50.812Z</v>
       </c>
       <c r="N33" t="str">
         <v/>
@@ -2150,19 +2150,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Astralis Talent</v>
+        <v>Misfits</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>2026-07-30T05:43:58.246Z</v>
       </c>
       <c r="N34" t="str">
         <v/>
@@ -2203,19 +2203,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Avangar</v>
+        <v>Kinguin</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>2026-07-30T05:44:09.112Z</v>
       </c>
       <c r="N35" t="str">
         <v/>
@@ -2256,19 +2256,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BIG Academy</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>2026-07-30T05:44:15.749Z</v>
       </c>
       <c r="N36" t="str">
         <v/>
@@ -2309,19 +2309,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bravado</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J37" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K37" t="str">
         <v>none</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>2026-07-30T05:44:22.588Z</v>
       </c>
       <c r="N37" t="str">
         <v/>
@@ -2362,19 +2362,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>2026-07-30T05:44:28.360Z</v>
       </c>
       <c r="N38" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENCE Academy</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>1000</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N39" t="str">
         <v/>
@@ -2468,19 +2468,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ESC</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>1000</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J40" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K40" t="str">
         <v>none</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N40" t="str">
         <v/>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Flash</v>
+        <v>TYLOO</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1000</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J41" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K41" t="str">
         <v>none</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N41" t="str">
         <v/>
@@ -2574,19 +2574,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>OG</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>1000</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N42" t="str">
         <v/>
@@ -2627,19 +2627,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>FlyQuest RED</v>
+        <v>BESTIA</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>1000</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J43" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K43" t="str">
         <v>none</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N43" t="str">
         <v/>
@@ -2680,19 +2680,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Fnatic</v>
+        <v>G2</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>1000</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N44" t="str">
         <v/>
@@ -2733,19 +2733,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FORZE</v>
+        <v>hoorai</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -2786,19 +2786,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Gambit</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1000</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>GATERON</v>
+        <v>Avangar</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>GhoulsW</v>
+        <v>Bravado</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J48" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K48" t="str">
         <v>none</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HAVU</v>
+        <v>FORZE</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J49" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K49" t="str">
         <v>none</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Heroic Academy</v>
+        <v>GATERON</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J50" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K50" t="str">
         <v>none</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Kinguin</v>
+        <v>kONO</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J52" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K52" t="str">
         <v>none</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>kONO</v>
+        <v>LGB</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>LGB</v>
+        <v>Rogue</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>MAD Lions</v>
+        <v>Shika</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J55" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K55" t="str">
         <v>none</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Misfits</v>
+        <v>Tsunami</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mousesports</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J57" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K57" t="str">
         <v>none</v>
@@ -3422,19 +3422,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MOUZ NXT</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J58" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K58" t="str">
         <v>none</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N58" t="str">
         <v/>
@@ -3475,19 +3475,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Movistar KOI</v>
+        <v>True Rippers</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N59" t="str">
         <v/>
@@ -3528,19 +3528,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>NIP Impact</v>
+        <v>FaZe</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N60" t="str">
         <v/>
@@ -3581,19 +3581,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nordix</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N61" t="str">
         <v/>
@@ -3634,19 +3634,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>NOVAQ</v>
+        <v>GODSENT</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J62" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K62" t="str">
         <v>none</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N62" t="str">
         <v/>
@@ -3687,19 +3687,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>QMISTRY</v>
+        <v>M80</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>1000</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J63" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K63" t="str">
         <v>none</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N63" t="str">
         <v/>
@@ -3740,19 +3740,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quantum Bellator Fire</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>1000</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J64" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K64" t="str">
         <v>none</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N64" t="str">
         <v/>
@@ -3793,19 +3793,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rogue</v>
+        <v>Orbit</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>1000</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J65" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K65" t="str">
         <v>none</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N65" t="str">
         <v/>
@@ -3846,19 +3846,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Shika</v>
+        <v>Alliance</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J66" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K66" t="str">
         <v>none</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N66" t="str">
         <v/>
@@ -3899,19 +3899,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SKYFURY</v>
+        <v>Homyno</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J67" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K67" t="str">
         <v>none</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N67" t="str">
         <v/>
@@ -3952,19 +3952,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Space Soldiers</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N68" t="str">
         <v/>
@@ -4005,19 +4005,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tsunami</v>
+        <v>Solid</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4032,7 +4032,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J69" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K69" t="str">
         <v>none</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N69" t="str">
         <v/>
@@ -4058,19 +4058,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>VeryGames</v>
+        <v>ENCE</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N70" t="str">
         <v/>
@@ -4111,19 +4111,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Vox Eminor</v>
+        <v>Nexus</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N71" t="str">
         <v/>
@@ -4164,19 +4164,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Wildcard Academy</v>
+        <v>MIBR</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>1000</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J72" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K72" t="str">
         <v>none</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N72" t="str">
         <v/>
@@ -4217,19 +4217,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lux Tenebris</v>
+        <v>Wizards</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>1000</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N73" t="str">
         <v/>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Spirit Academy</v>
+        <v>RED Canids</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74">
-        <v>999.7251809772306</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J74" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K74" t="str">
         <v>none</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4323,19 +4323,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>True Rippers</v>
+        <v>Rebels</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>999.7251809772306</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N75" t="str">
         <v/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>FaZe</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -4388,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="E76">
-        <v>999.7251809772306</v>
+        <v>996.0904918173039</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-07-23T22:12:51.919Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>iBUYPOWER</v>
+        <v>Mythic</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4438,10 +4438,10 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>999.7251809772306</v>
+        <v>986.2948766874508</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J77" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K77" t="str">
         <v>none</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-07-23T22:00:15.992Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,19 +4482,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>GODSENT</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>999.7251809772306</v>
+        <v>985</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J78" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K78" t="str">
         <v>none</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-07-30T05:44:28.360Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,19 +4535,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>M80</v>
+        <v>HAVU</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>999.672340544519</v>
+        <v>985</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J79" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K79" t="str">
         <v>none</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-07-30T05:44:22.588Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,19 +4588,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Chinggis Warriors</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>999.4408194717619</v>
+        <v>985</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-07-30T05:44:15.749Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Orbit</v>
+        <v>Flash</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>999.4186945376644</v>
+        <v>985</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-07-30T05:44:09.112Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alliance</v>
+        <v>ESC</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-07-30T05:43:58.246Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,19 +4747,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Homyno</v>
+        <v>00 Nation</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-07-30T05:43:50.812Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,19 +4800,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>MenaceGG</v>
+        <v>Quantum Bellator Fire</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-07-30T05:43:19.675Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,19 +4853,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Solid</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J85" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K85" t="str">
         <v>none</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-07-30T05:43:07.819Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,19 +4906,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ENCE</v>
+        <v>Nordix</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-07-30T05:42:58.796Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,19 +4959,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nexus</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-07-30T05:42:49.775Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,19 +5012,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>MIBR</v>
+        <v>QMISTRY</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>999.4088515186523</v>
+        <v>985</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-07-30T05:42:44.510Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,19 +5065,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Wizards</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>999.4062521695108</v>
+        <v>985</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J89" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K89" t="str">
         <v>none</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-07-30T05:42:06.941Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,19 +5118,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RED Canids</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>999.3397745397444</v>
+        <v>985</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J90" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K90" t="str">
         <v>none</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-07-30T05:41:55.808Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,19 +5171,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Rebels</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91">
-        <v>999.3232682842747</v>
+        <v>985</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-30T05:41:42.732Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,19 +5224,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Into the Beach</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92">
-        <v>996.0904918173039</v>
+        <v>985</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J92" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K92" t="str">
         <v>none</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-07-23T22:12:51.919Z</v>
+        <v>2026-07-30T05:39:19.440Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mythic</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>986.2948766874508</v>
+        <v>985</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J93" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K93" t="str">
         <v>none</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-07-23T22:00:15.992Z</v>
+        <v>2026-07-30T05:39:12.741Z</v>
       </c>
       <c r="N93" t="str">
         <v/>

--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_8827063FEF68FD417060021F3850A425A12DBD70" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DCACAE-83DF-4B09-8755-4379E7FC001F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_8827063FEF68FD417060021F3850A425A12DBD70" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58D24EA-3271-4926-B42D-AB565CE69DBC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1053,6 +1053,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1378,9 +1382,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q166"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1437,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1462,7 +1466,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -1486,7 +1490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1592,7 +1596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1645,7 +1649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1698,7 +1702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1751,7 +1755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1804,7 +1808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1857,7 +1861,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1910,7 +1914,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1963,7 +1967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -2016,7 +2020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -2069,7 +2073,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -2175,7 +2179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2228,7 +2232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2281,7 +2285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -2334,7 +2338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -2387,7 +2391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2440,7 +2444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2493,7 +2497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -2546,7 +2550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -2599,7 +2603,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -2652,7 +2656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -2705,7 +2709,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -2758,7 +2762,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -2811,7 +2815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>77</v>
       </c>
@@ -2864,7 +2868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -2917,7 +2921,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -2970,7 +2974,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -3023,7 +3027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>85</v>
       </c>
@@ -3076,7 +3080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -3129,7 +3133,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>89</v>
       </c>
@@ -3182,7 +3186,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>91</v>
       </c>
@@ -3235,7 +3239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -3288,7 +3292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>95</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>97</v>
       </c>
@@ -3394,7 +3398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -3447,7 +3451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -3500,7 +3504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>103</v>
       </c>
@@ -3553,7 +3557,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>105</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>107</v>
       </c>
@@ -3659,7 +3663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>109</v>
       </c>
@@ -3712,7 +3716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>111</v>
       </c>
@@ -3765,7 +3769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>113</v>
       </c>
@@ -3818,7 +3822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>114</v>
       </c>
@@ -3871,7 +3875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -3924,7 +3928,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>116</v>
       </c>
@@ -3977,7 +3981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>117</v>
       </c>
@@ -4030,7 +4034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -4083,7 +4087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>119</v>
       </c>
@@ -4136,7 +4140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>120</v>
       </c>
@@ -4189,7 +4193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -4242,7 +4246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -4295,7 +4299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -4348,7 +4352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -4401,7 +4405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>125</v>
       </c>
@@ -4454,7 +4458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -4507,7 +4511,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -4560,7 +4564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -4613,7 +4617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>133</v>
       </c>
@@ -4666,7 +4670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>135</v>
       </c>
@@ -4719,7 +4723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>137</v>
       </c>
@@ -4772,7 +4776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -4825,7 +4829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>141</v>
       </c>
@@ -4878,7 +4882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>143</v>
       </c>
@@ -4931,7 +4935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>145</v>
       </c>
@@ -4984,7 +4988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>147</v>
       </c>
@@ -5037,7 +5041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -5090,7 +5094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>151</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -5196,7 +5200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>155</v>
       </c>
@@ -5249,7 +5253,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>157</v>
       </c>
@@ -5302,7 +5306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>159</v>
       </c>
@@ -5355,7 +5359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -5408,7 +5412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -5461,7 +5465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -5514,7 +5518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>166</v>
       </c>
@@ -5567,7 +5571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>167</v>
       </c>
@@ -5620,7 +5624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -5673,7 +5677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>169</v>
       </c>
@@ -5726,7 +5730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -5779,7 +5783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>171</v>
       </c>
@@ -5832,7 +5836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>172</v>
       </c>
@@ -5885,7 +5889,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>173</v>
       </c>
@@ -5938,7 +5942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>174</v>
       </c>
@@ -5991,7 +5995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -6097,7 +6101,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>177</v>
       </c>
@@ -6150,7 +6154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -6203,7 +6207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>179</v>
       </c>
@@ -6256,7 +6260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>180</v>
       </c>
@@ -6309,7 +6313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>181</v>
       </c>
@@ -6362,7 +6366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>183</v>
       </c>
@@ -6415,7 +6419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>185</v>
       </c>
@@ -6468,7 +6472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>187</v>
       </c>
@@ -6521,7 +6525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>189</v>
       </c>
@@ -6574,7 +6578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>191</v>
       </c>
@@ -6627,7 +6631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>193</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>195</v>
       </c>
@@ -6733,7 +6737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -6786,7 +6790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>199</v>
       </c>
@@ -6839,7 +6843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>201</v>
       </c>
@@ -6892,7 +6896,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>203</v>
       </c>
@@ -6945,7 +6949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>205</v>
       </c>
@@ -6998,7 +7002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>207</v>
       </c>
@@ -7051,7 +7055,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>209</v>
       </c>
@@ -7104,7 +7108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>211</v>
       </c>
@@ -7157,7 +7161,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>213</v>
       </c>
@@ -7210,7 +7214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>215</v>
       </c>
@@ -7263,7 +7267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>217</v>
       </c>
@@ -7316,7 +7320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>219</v>
       </c>
@@ -7369,7 +7373,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>221</v>
       </c>
@@ -7422,7 +7426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>223</v>
       </c>
@@ -7475,7 +7479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>225</v>
       </c>
@@ -7528,7 +7532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>227</v>
       </c>
@@ -7581,7 +7585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>229</v>
       </c>
@@ -7634,7 +7638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>231</v>
       </c>
@@ -7687,7 +7691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>233</v>
       </c>
@@ -7740,7 +7744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>235</v>
       </c>
@@ -7793,7 +7797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>237</v>
       </c>
@@ -7846,7 +7850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>239</v>
       </c>
@@ -7899,7 +7903,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -7952,7 +7956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>243</v>
       </c>
@@ -8005,7 +8009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -8058,7 +8062,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>247</v>
       </c>
@@ -8111,7 +8115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>249</v>
       </c>
@@ -8164,7 +8168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>251</v>
       </c>
@@ -8217,7 +8221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>253</v>
       </c>
@@ -8270,7 +8274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>255</v>
       </c>
@@ -8323,7 +8327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>257</v>
       </c>
@@ -8376,7 +8380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>259</v>
       </c>
@@ -8429,7 +8433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>261</v>
       </c>
@@ -8482,7 +8486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>263</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>265</v>
       </c>
@@ -8588,7 +8592,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>267</v>
       </c>
@@ -8641,7 +8645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>269</v>
       </c>
@@ -8694,7 +8698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>271</v>
       </c>
@@ -8747,7 +8751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>273</v>
       </c>
@@ -8800,7 +8804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -8853,7 +8857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>277</v>
       </c>
@@ -8906,7 +8910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>279</v>
       </c>
@@ -8959,7 +8963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>281</v>
       </c>
@@ -9012,7 +9016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>283</v>
       </c>
@@ -9065,7 +9069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>285</v>
       </c>
@@ -9118,7 +9122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>287</v>
       </c>
@@ -9171,7 +9175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>289</v>
       </c>
@@ -9224,7 +9228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>291</v>
       </c>
@@ -9277,7 +9281,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>293</v>
       </c>
@@ -9330,7 +9334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>295</v>
       </c>
@@ -9383,7 +9387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>297</v>
       </c>
@@ -9436,7 +9440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>299</v>
       </c>
@@ -9489,7 +9493,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>301</v>
       </c>
@@ -9542,7 +9546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>303</v>
       </c>
@@ -9595,7 +9599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>305</v>
       </c>
@@ -9648,7 +9652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>307</v>
       </c>
@@ -9701,7 +9705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>309</v>
       </c>
@@ -9754,7 +9758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>311</v>
       </c>
@@ -9807,7 +9811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>313</v>
       </c>
@@ -9860,7 +9864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>315</v>
       </c>
@@ -9913,7 +9917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>317</v>
       </c>
@@ -9966,7 +9970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>319</v>
       </c>
@@ -10019,7 +10023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>321</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>323</v>
       </c>
@@ -10125,7 +10129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>325</v>
       </c>
@@ -10181,7 +10185,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q1 A3:Q166 A2:E2 G2:Q2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q1 A3:Q166 A2:E2 G2:I2 K2:Q2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/ranking.xlsx
+++ b/file/ranking.xlsx
@@ -772,19 +772,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Natus Vincere</v>
+        <v>Fnatic</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1064.5550904053082</v>
+        <v>1077.667615929619</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>Tier 3</v>
@@ -802,13 +802,13 @@
         <v>EU</v>
       </c>
       <c r="K8" t="str">
-        <v>none</v>
+        <v>regional</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-06-26T13:18:10.268Z</v>
+        <v>2026-08-23T07:39:51.003Z</v>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -825,19 +825,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Liquid</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>1064.3973274912723</v>
+        <v>1064.5550904053082</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-06-26T13:20:06.028Z</v>
+        <v>2026-06-26T13:18:10.268Z</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -878,19 +878,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Elevate</v>
+        <v>Liquid</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>1056.7441503790217</v>
+        <v>1064.3973274912723</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J10" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K10" t="str">
         <v>none</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-05-30T04:01:58.103Z</v>
+        <v>2026-06-26T13:20:06.028Z</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -931,7 +931,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Eternal Fire</v>
+        <v>Elevate</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -943,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>1055.7875002516132</v>
+        <v>1056.7441503790217</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J11" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K11" t="str">
         <v>none</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-05-30T04:01:51.528Z</v>
+        <v>2026-05-30T04:01:58.103Z</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -984,19 +984,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FURIA</v>
+        <v>Eternal Fire</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>1050.7178542874221</v>
+        <v>1055.7875002516132</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1005,22 +1005,22 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
         <v>Tier 3</v>
       </c>
       <c r="J12" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K12" t="str">
-        <v>regional</v>
+        <v>none</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-07-23T22:29:09.347Z</v>
+        <v>2026-05-30T04:01:51.528Z</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1037,19 +1037,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Titan</v>
+        <v>FURIA</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>1046.4273525065098</v>
+        <v>1050.7178542874221</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>Tier 3</v>
@@ -1067,13 +1067,13 @@
         <v>AM</v>
       </c>
       <c r="K13" t="str">
-        <v>none</v>
+        <v>regional</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-05-30T04:00:20.081Z</v>
+        <v>2026-07-23T22:29:09.347Z</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1090,19 +1090,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>AMKAL</v>
+        <v>Titan</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>1041.3191963490904</v>
+        <v>1046.4273525065098</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-07-23T22:16:25.593Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Verdant</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1038.7190184710753</v>
+        <v>1045.6755056188154</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-02-28T06:29:24.671Z</v>
+        <v>2026-08-23T07:39:22.255Z</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1196,19 +1196,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>PARIVISION</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>1034.630067328374</v>
+        <v>1045.0604120732232</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-05-01T06:07:06.437Z</v>
+        <v>2026-08-23T07:39:14.984Z</v>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -1249,19 +1249,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cloud9</v>
+        <v>AMKAL</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>1031.0582679094105</v>
+        <v>1041.3191963490904</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J17" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K17" t="str">
         <v>none</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-05-01T06:06:54.331Z</v>
+        <v>2026-07-23T22:16:25.593Z</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -1302,19 +1302,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Heroic</v>
+        <v>Verdant</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>1030.413991476608</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-05-01T06:08:21.905Z</v>
+        <v>2026-02-28T06:29:24.671Z</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1355,19 +1355,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Fnatic</v>
+        <v>PARIVISION</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>1030.2960629803374</v>
+        <v>1034.630067328374</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-08-08T06:03:54.346Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Cloud9</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>1030.2960629803374</v>
+        <v>1031.0582679094105</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J20" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K20" t="str">
         <v>none</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-08-08T06:04:14.871Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENCE Academy</v>
+        <v>Heroic</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>1030.2960629803374</v>
+        <v>1030.413991476608</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-08-08T06:04:29.697Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>BIG Academy</v>
+        <v>Entropiq</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>1030.2960629803374</v>
+        <v>1029.3999079514006</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J22" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K22" t="str">
         <v>none</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-08-08T06:04:44.394Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Wildcard Academy</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1030.2960629803374</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-08T06:05:55.763Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Astana Dragons</v>
+        <v>Spirit</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1030.2960629803374</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-08-08T06:06:03.563Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SKYFURY</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>2</v>
       </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
       <c r="E25">
-        <v>1030.2960629803374</v>
+        <v>1015.0604120732232</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-08T06:06:19.166Z</v>
+        <v>2026-08-23T07:39:14.984Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Vox Eminor</v>
+        <v>The Huns</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>1030.2960629803374</v>
+        <v>1015</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-08-08T06:10:52.072Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Entropiq</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>1029.3999079514006</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-07-23T22:14:26.816Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bounty Hunters</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>1017.2412711985547</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-08-23T07:38:19.410Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Spirit</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>1016.7402640066111</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-08-23T07:38:11.231Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>The Huns</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>1015</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-08-23T07:38:02.605Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Onyx Ravens</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>1014.9877256835035</v>
+        <v>1014.7261395369545</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J31" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K31" t="str">
         <v>none</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-08-23T07:37:55.979Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
